--- a/sequencer input v2.xlsx
+++ b/sequencer input v2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ui208936\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B95A6A13-5ACA-45A6-80C1-583A0FE0DB8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C7FA2A1-877B-4365-A6AD-EAE742E01576}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="-2832" windowWidth="30936" windowHeight="16776" xr2:uid="{45D2DF17-6F7C-45FD-9E14-08090A3A3102}"/>
+    <workbookView xWindow="-67320" yWindow="-3525" windowWidth="29040" windowHeight="15720" xr2:uid="{45D2DF17-6F7C-45FD-9E14-08090A3A3102}"/>
   </bookViews>
   <sheets>
     <sheet name="FOU data" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="976" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="976" uniqueCount="203">
   <si>
     <t>Structure</t>
   </si>
@@ -425,9 +425,6 @@
     <t>OSS</t>
   </si>
   <si>
-    <t>C05</t>
-  </si>
-  <si>
     <t>Jacking difficulty WTG</t>
   </si>
   <si>
@@ -524,45 +521,15 @@
     <t>D1:D04D-OSS</t>
   </si>
   <si>
-    <t>E1:OSS-C04E</t>
-  </si>
-  <si>
     <t>E</t>
   </si>
   <si>
     <t>EF</t>
   </si>
   <si>
-    <t>E2:C04E-C03E</t>
-  </si>
-  <si>
-    <t>E3:C03E-B02E</t>
-  </si>
-  <si>
-    <t>E4:B02E-A01E</t>
-  </si>
-  <si>
-    <t>E5:A01E-A02E</t>
-  </si>
-  <si>
-    <t>XEF:A02E-A03F</t>
-  </si>
-  <si>
-    <t>F5:A03F-B03F</t>
-  </si>
-  <si>
     <t>F</t>
   </si>
   <si>
-    <t>F4:B03F-B04F</t>
-  </si>
-  <si>
-    <t>F3:B04F-C05F</t>
-  </si>
-  <si>
-    <t>F2:C05F-D06F</t>
-  </si>
-  <si>
     <t>F1:D06F-OSS</t>
   </si>
   <si>
@@ -684,6 +651,36 @@
   </si>
   <si>
     <t>Nickname</t>
+  </si>
+  <si>
+    <t>E1:OSS-D05E</t>
+  </si>
+  <si>
+    <t>E2:D05E-C04E</t>
+  </si>
+  <si>
+    <t>E3:C04E-C03E</t>
+  </si>
+  <si>
+    <t>E4:C03E-B02E</t>
+  </si>
+  <si>
+    <t>E5:B02E-A01E</t>
+  </si>
+  <si>
+    <t>XEF:A01E-A02E</t>
+  </si>
+  <si>
+    <t>F5: A02E-A03F</t>
+  </si>
+  <si>
+    <t>F4:A03F-B03F</t>
+  </si>
+  <si>
+    <t>F3:B03F-B04F</t>
+  </si>
+  <si>
+    <t>F2:B04F-D06F</t>
   </si>
 </sst>
 </file>
@@ -1052,7 +1049,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1160,17 +1157,53 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1188,10 +1221,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1532,7 +1561,7 @@
         <v>58</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="C1" s="6" t="s">
         <v>0</v>
@@ -1547,10 +1576,10 @@
         <v>57</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="I1" s="6" t="s">
         <v>55</v>
@@ -1559,16 +1588,16 @@
         <v>54</v>
       </c>
       <c r="K1" s="6" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="L1" s="6" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="M1" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="N1" s="38" t="s">
-        <v>198</v>
+        <v>182</v>
+      </c>
+      <c r="N1" s="6" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.35">
@@ -3228,34 +3257,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="39" x14ac:dyDescent="0.35">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="B1" s="38" t="s">
+        <v>192</v>
+      </c>
+      <c r="C1" s="38" t="s">
+        <v>185</v>
+      </c>
+      <c r="D1" s="38" t="s">
         <v>119</v>
       </c>
-      <c r="B1" s="40" t="s">
-        <v>203</v>
-      </c>
-      <c r="C1" s="40" t="s">
-        <v>196</v>
-      </c>
-      <c r="D1" s="40" t="s">
+      <c r="E1" s="38" t="s">
         <v>120</v>
       </c>
-      <c r="E1" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="F1" s="40" t="s">
+      <c r="F1" s="38" t="s">
         <v>114</v>
       </c>
-      <c r="G1" s="40" t="s">
+      <c r="G1" s="38" t="s">
         <v>115</v>
       </c>
-      <c r="H1" s="40" t="s">
-        <v>202</v>
+      <c r="H1" s="38" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="32" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B2" s="32" t="str">
         <f>F2&amp;"-"&amp;G2</f>
@@ -3265,10 +3294,10 @@
         <v>56</v>
       </c>
       <c r="D2" s="32" t="s">
+        <v>122</v>
+      </c>
+      <c r="E2" s="33" t="s">
         <v>123</v>
-      </c>
-      <c r="E2" s="33" t="s">
-        <v>124</v>
       </c>
       <c r="F2" s="13" t="s">
         <v>116</v>
@@ -3276,13 +3305,13 @@
       <c r="G2" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="H2" s="39" t="s">
+      <c r="H2" s="37" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B3" s="28" t="str">
         <f t="shared" ref="B3:B56" si="0">F3&amp;"-"&amp;G3</f>
@@ -3292,10 +3321,10 @@
         <v>56</v>
       </c>
       <c r="D3" s="28" t="s">
+        <v>122</v>
+      </c>
+      <c r="E3" s="29" t="s">
         <v>123</v>
-      </c>
-      <c r="E3" s="29" t="s">
-        <v>124</v>
       </c>
       <c r="F3" s="11" t="s">
         <v>51</v>
@@ -3309,7 +3338,7 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="28" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B4" s="28" t="str">
         <f t="shared" si="0"/>
@@ -3319,10 +3348,10 @@
         <v>56</v>
       </c>
       <c r="D4" s="28" t="s">
+        <v>122</v>
+      </c>
+      <c r="E4" s="29" t="s">
         <v>123</v>
-      </c>
-      <c r="E4" s="29" t="s">
-        <v>124</v>
       </c>
       <c r="F4" s="11" t="s">
         <v>49</v>
@@ -3336,7 +3365,7 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="28" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B5" s="28" t="str">
         <f t="shared" si="0"/>
@@ -3346,10 +3375,10 @@
         <v>56</v>
       </c>
       <c r="D5" s="28" t="s">
+        <v>122</v>
+      </c>
+      <c r="E5" s="29" t="s">
         <v>123</v>
-      </c>
-      <c r="E5" s="29" t="s">
-        <v>124</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>48</v>
@@ -3363,7 +3392,7 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="28" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B6" s="28" t="str">
         <f t="shared" si="0"/>
@@ -3373,10 +3402,10 @@
         <v>56</v>
       </c>
       <c r="D6" s="28" t="s">
+        <v>122</v>
+      </c>
+      <c r="E6" s="29" t="s">
         <v>123</v>
-      </c>
-      <c r="E6" s="29" t="s">
-        <v>124</v>
       </c>
       <c r="F6" s="11" t="s">
         <v>47</v>
@@ -3390,7 +3419,7 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="28" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B7" s="28" t="str">
         <f t="shared" si="0"/>
@@ -3401,7 +3430,7 @@
       </c>
       <c r="D7" s="28"/>
       <c r="E7" s="29" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F7" s="11" t="s">
         <v>46</v>
@@ -3415,20 +3444,20 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="28" t="s">
+        <v>129</v>
+      </c>
+      <c r="B8" s="28" t="str">
+        <f t="shared" si="0"/>
+        <v>F03-E02</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D8" s="28" t="s">
         <v>130</v>
       </c>
-      <c r="B8" s="28" t="str">
-        <f t="shared" si="0"/>
-        <v>F03-E02</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="D8" s="28" t="s">
-        <v>131</v>
-      </c>
       <c r="E8" s="29" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F8" s="11" t="s">
         <v>40</v>
@@ -3442,7 +3471,7 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="28" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B9" s="28" t="str">
         <f t="shared" si="0"/>
@@ -3452,10 +3481,10 @@
         <v>56</v>
       </c>
       <c r="D9" s="28" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E9" s="29" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F9" s="11" t="s">
         <v>44</v>
@@ -3469,7 +3498,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="28" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B10" s="28" t="str">
         <f t="shared" si="0"/>
@@ -3479,10 +3508,10 @@
         <v>56</v>
       </c>
       <c r="D10" s="28" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E10" s="29" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F10" s="11" t="s">
         <v>30</v>
@@ -3496,7 +3525,7 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" s="28" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B11" s="28" t="str">
         <f t="shared" si="0"/>
@@ -3506,10 +3535,10 @@
         <v>56</v>
       </c>
       <c r="D11" s="28" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E11" s="29" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F11" s="11" t="s">
         <v>43</v>
@@ -3523,7 +3552,7 @@
     </row>
     <row r="12" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A12" s="30" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B12" s="30" t="str">
         <f t="shared" si="0"/>
@@ -3533,10 +3562,10 @@
         <v>56</v>
       </c>
       <c r="D12" s="30" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E12" s="31" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F12" s="12" t="s">
         <v>50</v>
@@ -3550,20 +3579,20 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" s="32" t="s">
+        <v>135</v>
+      </c>
+      <c r="B13" s="32" t="str">
+        <f t="shared" si="0"/>
+        <v>OSS-E06</v>
+      </c>
+      <c r="C13" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="D13" s="32" t="s">
         <v>136</v>
       </c>
-      <c r="B13" s="32" t="str">
-        <f t="shared" si="0"/>
-        <v>OSS-E06</v>
-      </c>
-      <c r="C13" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="D13" s="32" t="s">
+      <c r="E13" s="33" t="s">
         <v>137</v>
-      </c>
-      <c r="E13" s="33" t="s">
-        <v>138</v>
       </c>
       <c r="F13" s="13" t="s">
         <v>116</v>
@@ -3577,7 +3606,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="28" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B14" s="28" t="str">
         <f t="shared" si="0"/>
@@ -3587,10 +3616,10 @@
         <v>56</v>
       </c>
       <c r="D14" s="28" t="s">
+        <v>136</v>
+      </c>
+      <c r="E14" s="29" t="s">
         <v>137</v>
-      </c>
-      <c r="E14" s="29" t="s">
-        <v>138</v>
       </c>
       <c r="F14" s="11" t="s">
         <v>45</v>
@@ -3604,7 +3633,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" s="28" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B15" s="28" t="str">
         <f t="shared" si="0"/>
@@ -3614,10 +3643,10 @@
         <v>56</v>
       </c>
       <c r="D15" s="28" t="s">
+        <v>136</v>
+      </c>
+      <c r="E15" s="29" t="s">
         <v>137</v>
-      </c>
-      <c r="E15" s="29" t="s">
-        <v>138</v>
       </c>
       <c r="F15" s="11" t="s">
         <v>36</v>
@@ -3631,7 +3660,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" s="28" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B16" s="28" t="str">
         <f t="shared" si="0"/>
@@ -3641,10 +3670,10 @@
         <v>56</v>
       </c>
       <c r="D16" s="28" t="s">
+        <v>136</v>
+      </c>
+      <c r="E16" s="29" t="s">
         <v>137</v>
-      </c>
-      <c r="E16" s="29" t="s">
-        <v>138</v>
       </c>
       <c r="F16" s="11" t="s">
         <v>37</v>
@@ -3658,7 +3687,7 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" s="28" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B17" s="28" t="str">
         <f t="shared" si="0"/>
@@ -3668,10 +3697,10 @@
         <v>56</v>
       </c>
       <c r="D17" s="28" t="s">
+        <v>136</v>
+      </c>
+      <c r="E17" s="29" t="s">
         <v>137</v>
-      </c>
-      <c r="E17" s="29" t="s">
-        <v>138</v>
       </c>
       <c r="F17" s="11" t="s">
         <v>6</v>
@@ -3685,7 +3714,7 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" s="28" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B18" s="28" t="str">
         <f t="shared" si="0"/>
@@ -3696,7 +3725,7 @@
       </c>
       <c r="D18" s="28"/>
       <c r="E18" s="29" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F18" s="11" t="s">
         <v>38</v>
@@ -3710,20 +3739,20 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" s="28" t="s">
+        <v>143</v>
+      </c>
+      <c r="B19" s="28" t="str">
+        <f t="shared" si="0"/>
+        <v>C01-B01</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D19" s="28" t="s">
         <v>144</v>
       </c>
-      <c r="B19" s="28" t="str">
-        <f t="shared" si="0"/>
-        <v>C01-B01</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="D19" s="28" t="s">
-        <v>145</v>
-      </c>
       <c r="E19" s="29" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F19" s="11" t="s">
         <v>22</v>
@@ -3737,7 +3766,7 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" s="28" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B20" s="28" t="str">
         <f t="shared" si="0"/>
@@ -3747,10 +3776,10 @@
         <v>56</v>
       </c>
       <c r="D20" s="28" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E20" s="29" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F20" s="11" t="s">
         <v>18</v>
@@ -3764,7 +3793,7 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" s="28" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B21" s="28" t="str">
         <f t="shared" si="0"/>
@@ -3774,10 +3803,10 @@
         <v>56</v>
       </c>
       <c r="D21" s="28" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E21" s="29" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F21" s="11" t="s">
         <v>27</v>
@@ -3791,7 +3820,7 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" s="28" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B22" s="28" t="str">
         <f t="shared" si="0"/>
@@ -3801,10 +3830,10 @@
         <v>56</v>
       </c>
       <c r="D22" s="28" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E22" s="29" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F22" s="11" t="s">
         <v>31</v>
@@ -3818,7 +3847,7 @@
     </row>
     <row r="23" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A23" s="34" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B23" s="34" t="str">
         <f t="shared" si="0"/>
@@ -3828,10 +3857,10 @@
         <v>56</v>
       </c>
       <c r="D23" s="34" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E23" s="35" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F23" s="14" t="s">
         <v>39</v>
@@ -3844,303 +3873,303 @@
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A24" s="26" t="s">
+      <c r="A24" s="40" t="s">
+        <v>193</v>
+      </c>
+      <c r="B24" s="40" t="str">
+        <f t="shared" si="0"/>
+        <v>OSS-D05</v>
+      </c>
+      <c r="C24" s="40" t="s">
+        <v>56</v>
+      </c>
+      <c r="D24" s="40" t="s">
+        <v>149</v>
+      </c>
+      <c r="E24" s="41" t="s">
         <v>150</v>
       </c>
-      <c r="B24" s="26" t="str">
-        <f t="shared" si="0"/>
-        <v>OSS-C04</v>
-      </c>
-      <c r="C24" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="D24" s="26" t="s">
+      <c r="F24" s="40" t="s">
+        <v>116</v>
+      </c>
+      <c r="G24" s="40" t="s">
+        <v>53</v>
+      </c>
+      <c r="H24" s="42" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A25" s="43" t="s">
+        <v>194</v>
+      </c>
+      <c r="B25" s="43" t="str">
+        <f t="shared" si="0"/>
+        <v>D05-C04</v>
+      </c>
+      <c r="C25" s="44" t="s">
+        <v>56</v>
+      </c>
+      <c r="D25" s="43" t="s">
+        <v>149</v>
+      </c>
+      <c r="E25" s="45" t="s">
+        <v>150</v>
+      </c>
+      <c r="F25" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="G25" s="43" t="s">
+        <v>26</v>
+      </c>
+      <c r="H25" s="42" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A26" s="43" t="s">
+        <v>195</v>
+      </c>
+      <c r="B26" s="43" t="str">
+        <f t="shared" si="0"/>
+        <v>C04-C03</v>
+      </c>
+      <c r="C26" s="44" t="s">
+        <v>56</v>
+      </c>
+      <c r="D26" s="43" t="s">
+        <v>149</v>
+      </c>
+      <c r="E26" s="45" t="s">
+        <v>150</v>
+      </c>
+      <c r="F26" s="44" t="s">
+        <v>26</v>
+      </c>
+      <c r="G26" s="43" t="s">
+        <v>34</v>
+      </c>
+      <c r="H26" s="42" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A27" s="43" t="s">
+        <v>196</v>
+      </c>
+      <c r="B27" s="43" t="str">
+        <f t="shared" si="0"/>
+        <v>C03-B02</v>
+      </c>
+      <c r="C27" s="44" t="s">
+        <v>56</v>
+      </c>
+      <c r="D27" s="43" t="s">
+        <v>149</v>
+      </c>
+      <c r="E27" s="45" t="s">
+        <v>150</v>
+      </c>
+      <c r="F27" s="46" t="s">
+        <v>34</v>
+      </c>
+      <c r="G27" s="47" t="s">
+        <v>11</v>
+      </c>
+      <c r="H27" s="42" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A28" s="43" t="s">
+        <v>197</v>
+      </c>
+      <c r="B28" s="43" t="str">
+        <f t="shared" si="0"/>
+        <v>B02-A01</v>
+      </c>
+      <c r="C28" s="44" t="s">
+        <v>56</v>
+      </c>
+      <c r="D28" s="43" t="s">
+        <v>149</v>
+      </c>
+      <c r="E28" s="45" t="s">
+        <v>150</v>
+      </c>
+      <c r="F28" s="46" t="s">
+        <v>11</v>
+      </c>
+      <c r="G28" s="47" t="s">
+        <v>14</v>
+      </c>
+      <c r="H28" s="42" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A29" s="43" t="s">
+        <v>198</v>
+      </c>
+      <c r="B29" s="43" t="str">
+        <f t="shared" si="0"/>
+        <v>A01-A02</v>
+      </c>
+      <c r="C29" s="44" t="s">
+        <v>56</v>
+      </c>
+      <c r="D29" s="43"/>
+      <c r="E29" s="45" t="s">
+        <v>150</v>
+      </c>
+      <c r="F29" s="46" t="s">
+        <v>14</v>
+      </c>
+      <c r="G29" s="47" t="s">
+        <v>8</v>
+      </c>
+      <c r="H29" s="42" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A30" s="43" t="s">
+        <v>199</v>
+      </c>
+      <c r="B30" s="43" t="str">
+        <f t="shared" si="0"/>
+        <v>A02-A03</v>
+      </c>
+      <c r="C30" s="44" t="s">
+        <v>56</v>
+      </c>
+      <c r="D30" s="43" t="s">
         <v>151</v>
       </c>
-      <c r="E24" s="27" t="s">
+      <c r="E30" s="45" t="s">
+        <v>150</v>
+      </c>
+      <c r="F30" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="G30" s="47" t="s">
+        <v>5</v>
+      </c>
+      <c r="H30" s="42" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A31" s="43" t="s">
+        <v>200</v>
+      </c>
+      <c r="B31" s="43" t="str">
+        <f t="shared" si="0"/>
+        <v>A03-B03</v>
+      </c>
+      <c r="C31" s="44" t="s">
+        <v>56</v>
+      </c>
+      <c r="D31" s="43" t="s">
+        <v>151</v>
+      </c>
+      <c r="E31" s="45" t="s">
+        <v>150</v>
+      </c>
+      <c r="F31" s="46" t="s">
+        <v>5</v>
+      </c>
+      <c r="G31" s="47" t="s">
+        <v>12</v>
+      </c>
+      <c r="H31" s="42" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A32" s="43" t="s">
+        <v>201</v>
+      </c>
+      <c r="B32" s="43" t="str">
+        <f t="shared" si="0"/>
+        <v>B03-B04</v>
+      </c>
+      <c r="C32" s="44" t="s">
+        <v>56</v>
+      </c>
+      <c r="D32" s="43" t="s">
+        <v>151</v>
+      </c>
+      <c r="E32" s="45" t="s">
+        <v>150</v>
+      </c>
+      <c r="F32" s="46" t="s">
+        <v>12</v>
+      </c>
+      <c r="G32" s="47" t="s">
+        <v>15</v>
+      </c>
+      <c r="H32" s="42" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A33" s="43" t="s">
+        <v>202</v>
+      </c>
+      <c r="B33" s="43" t="str">
+        <f t="shared" si="0"/>
+        <v>B04-D06</v>
+      </c>
+      <c r="C33" s="44" t="s">
+        <v>56</v>
+      </c>
+      <c r="D33" s="43" t="s">
+        <v>151</v>
+      </c>
+      <c r="E33" s="45" t="s">
+        <v>150</v>
+      </c>
+      <c r="F33" s="46" t="s">
+        <v>15</v>
+      </c>
+      <c r="G33" s="47" t="s">
+        <v>42</v>
+      </c>
+      <c r="H33" s="42" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A34" s="48" t="s">
         <v>152</v>
       </c>
-      <c r="F24" s="10" t="s">
+      <c r="B34" s="48" t="str">
+        <f t="shared" si="0"/>
+        <v>D06-OSS</v>
+      </c>
+      <c r="C34" s="49" t="s">
+        <v>56</v>
+      </c>
+      <c r="D34" s="48" t="s">
+        <v>151</v>
+      </c>
+      <c r="E34" s="50" t="s">
+        <v>150</v>
+      </c>
+      <c r="F34" s="51" t="s">
+        <v>42</v>
+      </c>
+      <c r="G34" s="52" t="s">
         <v>116</v>
       </c>
-      <c r="G24" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="H24" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A25" s="28" t="s">
-        <v>153</v>
-      </c>
-      <c r="B25" s="28" t="str">
-        <f t="shared" si="0"/>
-        <v>C04-C03</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="D25" s="28" t="s">
-        <v>151</v>
-      </c>
-      <c r="E25" s="29" t="s">
-        <v>152</v>
-      </c>
-      <c r="F25" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="G25" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="H25" s="4" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A26" s="28" t="s">
-        <v>154</v>
-      </c>
-      <c r="B26" s="28" t="str">
-        <f t="shared" si="0"/>
-        <v>C03-B02</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="D26" s="28" t="s">
-        <v>151</v>
-      </c>
-      <c r="E26" s="29" t="s">
-        <v>152</v>
-      </c>
-      <c r="F26" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="G26" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="H26" s="4" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A27" s="28" t="s">
-        <v>155</v>
-      </c>
-      <c r="B27" s="28" t="str">
-        <f t="shared" si="0"/>
-        <v>B02-A01</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="D27" s="28" t="s">
-        <v>151</v>
-      </c>
-      <c r="E27" s="29" t="s">
-        <v>152</v>
-      </c>
-      <c r="F27" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="G27" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="H27" s="4" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A28" s="28" t="s">
-        <v>156</v>
-      </c>
-      <c r="B28" s="28" t="str">
-        <f t="shared" si="0"/>
-        <v>A01-A02</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="D28" s="28" t="s">
-        <v>151</v>
-      </c>
-      <c r="E28" s="29" t="s">
-        <v>152</v>
-      </c>
-      <c r="F28" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="G28" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="H28" s="4" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A29" s="28" t="s">
-        <v>157</v>
-      </c>
-      <c r="B29" s="28" t="str">
-        <f t="shared" si="0"/>
-        <v>A02-A03</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="D29" s="28"/>
-      <c r="E29" s="29" t="s">
-        <v>152</v>
-      </c>
-      <c r="F29" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="G29" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="H29" s="4" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A30" s="28" t="s">
-        <v>158</v>
-      </c>
-      <c r="B30" s="28" t="str">
-        <f t="shared" si="0"/>
-        <v>A03-B03</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="D30" s="28" t="s">
-        <v>159</v>
-      </c>
-      <c r="E30" s="29" t="s">
-        <v>152</v>
-      </c>
-      <c r="F30" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="G30" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="H30" s="4" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A31" s="28" t="s">
-        <v>160</v>
-      </c>
-      <c r="B31" s="28" t="str">
-        <f t="shared" si="0"/>
-        <v>B03-B04</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="D31" s="28" t="s">
-        <v>159</v>
-      </c>
-      <c r="E31" s="29" t="s">
-        <v>152</v>
-      </c>
-      <c r="F31" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G31" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="H31" s="4" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A32" s="28" t="s">
-        <v>161</v>
-      </c>
-      <c r="B32" s="28" t="str">
-        <f t="shared" si="0"/>
-        <v>B04-C05</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="D32" s="28" t="s">
-        <v>159</v>
-      </c>
-      <c r="E32" s="29" t="s">
-        <v>152</v>
-      </c>
-      <c r="F32" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G32" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="H32" s="4" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A33" s="28" t="s">
-        <v>162</v>
-      </c>
-      <c r="B33" s="28" t="str">
-        <f t="shared" si="0"/>
-        <v>C05-D06</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="D33" s="28" t="s">
-        <v>159</v>
-      </c>
-      <c r="E33" s="29" t="s">
-        <v>152</v>
-      </c>
-      <c r="F33" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="G33" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="H33" s="4" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="30" t="s">
-        <v>163</v>
-      </c>
-      <c r="B34" s="30" t="str">
-        <f t="shared" si="0"/>
-        <v>D06-OSS</v>
-      </c>
-      <c r="C34" s="34" t="s">
-        <v>56</v>
-      </c>
-      <c r="D34" s="30" t="s">
-        <v>159</v>
-      </c>
-      <c r="E34" s="31" t="s">
-        <v>152</v>
-      </c>
-      <c r="F34" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="G34" s="18" t="s">
-        <v>116</v>
-      </c>
-      <c r="H34" s="4" t="s">
+      <c r="H34" s="42" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A35" s="32" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="B35" s="32" t="str">
         <f t="shared" si="0"/>
@@ -4150,10 +4179,10 @@
         <v>56</v>
       </c>
       <c r="D35" s="32" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="E35" s="33" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="F35" s="13" t="s">
         <v>116</v>
@@ -4167,7 +4196,7 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A36" s="28" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="B36" s="28" t="str">
         <f t="shared" si="0"/>
@@ -4177,10 +4206,10 @@
         <v>56</v>
       </c>
       <c r="D36" s="28" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="E36" s="29" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="F36" s="11" t="s">
         <v>7</v>
@@ -4194,7 +4223,7 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A37" s="28" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="B37" s="28" t="str">
         <f t="shared" si="0"/>
@@ -4204,10 +4233,10 @@
         <v>56</v>
       </c>
       <c r="D37" s="28" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="E37" s="29" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="F37" s="11" t="s">
         <v>21</v>
@@ -4221,7 +4250,7 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A38" s="28" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="B38" s="28" t="str">
         <f t="shared" si="0"/>
@@ -4231,10 +4260,10 @@
         <v>56</v>
       </c>
       <c r="D38" s="28" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="E38" s="29" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="F38" s="11" t="s">
         <v>16</v>
@@ -4248,7 +4277,7 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A39" s="28" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="B39" s="28" t="str">
         <f t="shared" si="0"/>
@@ -4258,10 +4287,10 @@
         <v>56</v>
       </c>
       <c r="D39" s="28" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="E39" s="29" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="F39" s="11" t="s">
         <v>4</v>
@@ -4275,7 +4304,7 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A40" s="28" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="B40" s="28" t="str">
         <f t="shared" si="0"/>
@@ -4286,7 +4315,7 @@
       </c>
       <c r="D40" s="28"/>
       <c r="E40" s="29" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="F40" s="11" t="s">
         <v>10</v>
@@ -4300,7 +4329,7 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A41" s="28" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="B41" s="28" t="str">
         <f t="shared" si="0"/>
@@ -4310,10 +4339,10 @@
         <v>56</v>
       </c>
       <c r="D41" s="28" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="E41" s="29" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="F41" s="11" t="s">
         <v>17</v>
@@ -4327,7 +4356,7 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A42" s="28" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="B42" s="28" t="str">
         <f t="shared" si="0"/>
@@ -4337,10 +4366,10 @@
         <v>56</v>
       </c>
       <c r="D42" s="28" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="E42" s="29" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="F42" s="11" t="s">
         <v>20</v>
@@ -4354,7 +4383,7 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A43" s="28" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="B43" s="28" t="str">
         <f t="shared" si="0"/>
@@ -4364,10 +4393,10 @@
         <v>56</v>
       </c>
       <c r="D43" s="28" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="E43" s="29" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="F43" s="11" t="s">
         <v>9</v>
@@ -4381,7 +4410,7 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A44" s="28" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="B44" s="28" t="str">
         <f t="shared" si="0"/>
@@ -4391,10 +4420,10 @@
         <v>56</v>
       </c>
       <c r="D44" s="28" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="E44" s="29" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="F44" s="11" t="s">
         <v>13</v>
@@ -4408,7 +4437,7 @@
     </row>
     <row r="45" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A45" s="34" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="B45" s="34" t="str">
         <f t="shared" si="0"/>
@@ -4418,10 +4447,10 @@
         <v>56</v>
       </c>
       <c r="D45" s="34" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="E45" s="35" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="F45" s="14" t="s">
         <v>41</v>
@@ -4435,7 +4464,7 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A46" s="26" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="B46" s="26" t="str">
         <f t="shared" si="0"/>
@@ -4445,10 +4474,10 @@
         <v>56</v>
       </c>
       <c r="D46" s="26" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="E46" s="27" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="F46" s="10" t="s">
         <v>116</v>
@@ -4462,7 +4491,7 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A47" s="28" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="B47" s="28" t="str">
         <f t="shared" si="0"/>
@@ -4472,10 +4501,10 @@
         <v>56</v>
       </c>
       <c r="D47" s="28" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="E47" s="29" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="F47" s="11" t="s">
         <v>23</v>
@@ -4489,7 +4518,7 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A48" s="28" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="B48" s="28" t="str">
         <f t="shared" si="0"/>
@@ -4499,10 +4528,10 @@
         <v>56</v>
       </c>
       <c r="D48" s="28" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="E48" s="29" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="F48" s="11" t="s">
         <v>19</v>
@@ -4516,7 +4545,7 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A49" s="28" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="B49" s="28" t="str">
         <f t="shared" si="0"/>
@@ -4526,10 +4555,10 @@
         <v>56</v>
       </c>
       <c r="D49" s="28" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="E49" s="29" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="F49" s="11" t="s">
         <v>35</v>
@@ -4543,7 +4572,7 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A50" s="28" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="B50" s="28" t="str">
         <f t="shared" si="0"/>
@@ -4553,10 +4582,10 @@
         <v>56</v>
       </c>
       <c r="D50" s="28" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="E50" s="29" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="F50" s="11" t="s">
         <v>29</v>
@@ -4570,7 +4599,7 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A51" s="28" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="B51" s="28" t="str">
         <f t="shared" si="0"/>
@@ -4581,7 +4610,7 @@
       </c>
       <c r="D51" s="28"/>
       <c r="E51" s="29" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="F51" s="11" t="s">
         <v>24</v>
@@ -4595,7 +4624,7 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A52" s="28" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="B52" s="28" t="str">
         <f t="shared" si="0"/>
@@ -4605,10 +4634,10 @@
         <v>56</v>
       </c>
       <c r="D52" s="28" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="E52" s="29" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="F52" s="11" t="s">
         <v>28</v>
@@ -4622,7 +4651,7 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A53" s="28" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="B53" s="28" t="str">
         <f t="shared" si="0"/>
@@ -4632,10 +4661,10 @@
         <v>56</v>
       </c>
       <c r="D53" s="28" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="E53" s="29" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="F53" s="11" t="s">
         <v>32</v>
@@ -4649,7 +4678,7 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A54" s="28" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="B54" s="28" t="str">
         <f t="shared" si="0"/>
@@ -4659,10 +4688,10 @@
         <v>56</v>
       </c>
       <c r="D54" s="28" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="E54" s="29" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="F54" s="11" t="s">
         <v>25</v>
@@ -4676,7 +4705,7 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A55" s="28" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="B55" s="28" t="str">
         <f t="shared" si="0"/>
@@ -4686,10 +4715,10 @@
         <v>56</v>
       </c>
       <c r="D55" s="28" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="E55" s="29" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="F55" s="11" t="s">
         <v>33</v>
@@ -4703,7 +4732,7 @@
     </row>
     <row r="56" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A56" s="30" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="B56" s="30" t="str">
         <f t="shared" si="0"/>
@@ -4713,10 +4742,10 @@
         <v>56</v>
       </c>
       <c r="D56" s="30" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="E56" s="31" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="F56" s="12" t="s">
         <v>52</v>
@@ -4756,7 +4785,7 @@
         <v>58</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="C1" s="6" t="s">
         <v>0</v>
@@ -4774,7 +4803,7 @@
         <v>111</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
@@ -6126,40 +6155,40 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="23"/>
-      <c r="B1" s="37" t="s">
+      <c r="B1" s="39" t="s">
         <v>59</v>
       </c>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37" t="s">
+      <c r="C1" s="39"/>
+      <c r="D1" s="39" t="s">
         <v>60</v>
       </c>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1" s="37"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="39"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
@@ -6170,14 +6199,14 @@
         <v>47574</v>
       </c>
       <c r="C3" s="9">
-        <f>B3+1</f>
+        <f t="shared" ref="C3:C34" si="0">B3+1</f>
         <v>47575</v>
       </c>
       <c r="D3" s="25">
         <v>47696</v>
       </c>
       <c r="E3" s="25">
-        <f>D3+0.7</f>
+        <f t="shared" ref="E3:E34" si="1">D3+0.7</f>
         <v>47696.7</v>
       </c>
       <c r="F3" s="9">
@@ -6193,27 +6222,27 @@
         <v>2</v>
       </c>
       <c r="B4" s="9">
-        <f>B3+1</f>
+        <f t="shared" ref="B4:B35" si="2">B3+1</f>
         <v>47575</v>
       </c>
       <c r="C4" s="9">
-        <f>B4+1</f>
+        <f t="shared" si="0"/>
         <v>47576</v>
       </c>
       <c r="D4" s="9">
-        <f>D3+0.7</f>
+        <f t="shared" ref="D4:D35" si="3">D3+0.7</f>
         <v>47696.7</v>
       </c>
       <c r="E4" s="9">
-        <f>D4+0.7</f>
+        <f t="shared" si="1"/>
         <v>47697.399999999994</v>
       </c>
       <c r="F4" s="9">
-        <f>F3+4</f>
+        <f t="shared" ref="F4:F35" si="4">F3+4</f>
         <v>47912</v>
       </c>
       <c r="G4" s="9">
-        <f>G3+4</f>
+        <f t="shared" ref="G4:G35" si="5">G3+4</f>
         <v>47916</v>
       </c>
     </row>
@@ -6222,27 +6251,27 @@
         <v>3</v>
       </c>
       <c r="B5" s="9">
-        <f>B4+1</f>
+        <f t="shared" si="2"/>
         <v>47576</v>
       </c>
       <c r="C5" s="9">
-        <f>B5+1</f>
+        <f t="shared" si="0"/>
         <v>47577</v>
       </c>
       <c r="D5" s="9">
-        <f>D4+0.7</f>
+        <f t="shared" si="3"/>
         <v>47697.399999999994</v>
       </c>
       <c r="E5" s="9">
-        <f>D5+0.7</f>
+        <f t="shared" si="1"/>
         <v>47698.099999999991</v>
       </c>
       <c r="F5" s="9">
-        <f>F4+4</f>
+        <f t="shared" si="4"/>
         <v>47916</v>
       </c>
       <c r="G5" s="9">
-        <f>G4+4</f>
+        <f t="shared" si="5"/>
         <v>47920</v>
       </c>
     </row>
@@ -6251,27 +6280,27 @@
         <v>4</v>
       </c>
       <c r="B6" s="9">
-        <f>B5+1</f>
+        <f t="shared" si="2"/>
         <v>47577</v>
       </c>
       <c r="C6" s="9">
-        <f>B6+1</f>
+        <f t="shared" si="0"/>
         <v>47578</v>
       </c>
       <c r="D6" s="9">
-        <f>D5+0.7</f>
+        <f t="shared" si="3"/>
         <v>47698.099999999991</v>
       </c>
       <c r="E6" s="9">
-        <f>D6+0.7</f>
+        <f t="shared" si="1"/>
         <v>47698.799999999988</v>
       </c>
       <c r="F6" s="9">
-        <f>F5+4</f>
+        <f t="shared" si="4"/>
         <v>47920</v>
       </c>
       <c r="G6" s="9">
-        <f>G5+4</f>
+        <f t="shared" si="5"/>
         <v>47924</v>
       </c>
     </row>
@@ -6280,27 +6309,27 @@
         <v>5</v>
       </c>
       <c r="B7" s="9">
-        <f>B6+1</f>
+        <f t="shared" si="2"/>
         <v>47578</v>
       </c>
       <c r="C7" s="9">
-        <f>B7+1</f>
+        <f t="shared" si="0"/>
         <v>47579</v>
       </c>
       <c r="D7" s="9">
-        <f>D6+0.7</f>
+        <f t="shared" si="3"/>
         <v>47698.799999999988</v>
       </c>
       <c r="E7" s="9">
-        <f>D7+0.7</f>
+        <f t="shared" si="1"/>
         <v>47699.499999999985</v>
       </c>
       <c r="F7" s="9">
-        <f>F6+4</f>
+        <f t="shared" si="4"/>
         <v>47924</v>
       </c>
       <c r="G7" s="9">
-        <f>G6+4</f>
+        <f t="shared" si="5"/>
         <v>47928</v>
       </c>
     </row>
@@ -6309,27 +6338,27 @@
         <v>6</v>
       </c>
       <c r="B8" s="9">
-        <f>B7+1</f>
+        <f t="shared" si="2"/>
         <v>47579</v>
       </c>
       <c r="C8" s="9">
-        <f>B8+1</f>
+        <f t="shared" si="0"/>
         <v>47580</v>
       </c>
       <c r="D8" s="9">
-        <f>D7+0.7</f>
+        <f t="shared" si="3"/>
         <v>47699.499999999985</v>
       </c>
       <c r="E8" s="9">
-        <f>D8+0.7</f>
+        <f t="shared" si="1"/>
         <v>47700.199999999983</v>
       </c>
       <c r="F8" s="9">
-        <f>F7+4</f>
+        <f t="shared" si="4"/>
         <v>47928</v>
       </c>
       <c r="G8" s="9">
-        <f>G7+4</f>
+        <f t="shared" si="5"/>
         <v>47932</v>
       </c>
     </row>
@@ -6338,27 +6367,27 @@
         <v>7</v>
       </c>
       <c r="B9" s="9">
-        <f>B8+1</f>
+        <f t="shared" si="2"/>
         <v>47580</v>
       </c>
       <c r="C9" s="9">
-        <f>B9+1</f>
+        <f t="shared" si="0"/>
         <v>47581</v>
       </c>
       <c r="D9" s="9">
-        <f>D8+0.7</f>
+        <f t="shared" si="3"/>
         <v>47700.199999999983</v>
       </c>
       <c r="E9" s="9">
-        <f>D9+0.7</f>
+        <f t="shared" si="1"/>
         <v>47700.89999999998</v>
       </c>
       <c r="F9" s="9">
-        <f>F8+4</f>
+        <f t="shared" si="4"/>
         <v>47932</v>
       </c>
       <c r="G9" s="9">
-        <f>G8+4</f>
+        <f t="shared" si="5"/>
         <v>47936</v>
       </c>
     </row>
@@ -6367,27 +6396,27 @@
         <v>8</v>
       </c>
       <c r="B10" s="9">
-        <f>B9+1</f>
+        <f t="shared" si="2"/>
         <v>47581</v>
       </c>
       <c r="C10" s="9">
-        <f>B10+1</f>
+        <f t="shared" si="0"/>
         <v>47582</v>
       </c>
       <c r="D10" s="9">
-        <f>D9+0.7</f>
+        <f t="shared" si="3"/>
         <v>47700.89999999998</v>
       </c>
       <c r="E10" s="9">
-        <f>D10+0.7</f>
+        <f t="shared" si="1"/>
         <v>47701.599999999977</v>
       </c>
       <c r="F10" s="9">
-        <f>F9+4</f>
+        <f t="shared" si="4"/>
         <v>47936</v>
       </c>
       <c r="G10" s="9">
-        <f>G9+4</f>
+        <f t="shared" si="5"/>
         <v>47940</v>
       </c>
     </row>
@@ -6396,27 +6425,27 @@
         <v>9</v>
       </c>
       <c r="B11" s="9">
-        <f>B10+1</f>
+        <f t="shared" si="2"/>
         <v>47582</v>
       </c>
       <c r="C11" s="9">
-        <f>B11+1</f>
+        <f t="shared" si="0"/>
         <v>47583</v>
       </c>
       <c r="D11" s="9">
-        <f>D10+0.7</f>
+        <f t="shared" si="3"/>
         <v>47701.599999999977</v>
       </c>
       <c r="E11" s="9">
-        <f>D11+0.7</f>
+        <f t="shared" si="1"/>
         <v>47702.299999999974</v>
       </c>
       <c r="F11" s="9">
-        <f>F10+4</f>
+        <f t="shared" si="4"/>
         <v>47940</v>
       </c>
       <c r="G11" s="9">
-        <f>G10+4</f>
+        <f t="shared" si="5"/>
         <v>47944</v>
       </c>
     </row>
@@ -6425,27 +6454,27 @@
         <v>10</v>
       </c>
       <c r="B12" s="9">
-        <f>B11+1</f>
+        <f t="shared" si="2"/>
         <v>47583</v>
       </c>
       <c r="C12" s="9">
-        <f>B12+1</f>
+        <f t="shared" si="0"/>
         <v>47584</v>
       </c>
       <c r="D12" s="9">
-        <f>D11+0.7</f>
+        <f t="shared" si="3"/>
         <v>47702.299999999974</v>
       </c>
       <c r="E12" s="9">
-        <f>D12+0.7</f>
+        <f t="shared" si="1"/>
         <v>47702.999999999971</v>
       </c>
       <c r="F12" s="9">
-        <f>F11+4</f>
+        <f t="shared" si="4"/>
         <v>47944</v>
       </c>
       <c r="G12" s="9">
-        <f>G11+4</f>
+        <f t="shared" si="5"/>
         <v>47948</v>
       </c>
     </row>
@@ -6454,27 +6483,27 @@
         <v>11</v>
       </c>
       <c r="B13" s="9">
-        <f>B12+1</f>
+        <f t="shared" si="2"/>
         <v>47584</v>
       </c>
       <c r="C13" s="9">
-        <f>B13+1</f>
+        <f t="shared" si="0"/>
         <v>47585</v>
       </c>
       <c r="D13" s="9">
-        <f>D12+0.7</f>
+        <f t="shared" si="3"/>
         <v>47702.999999999971</v>
       </c>
       <c r="E13" s="9">
-        <f>D13+0.7</f>
+        <f t="shared" si="1"/>
         <v>47703.699999999968</v>
       </c>
       <c r="F13" s="9">
-        <f>F12+4</f>
+        <f t="shared" si="4"/>
         <v>47948</v>
       </c>
       <c r="G13" s="9">
-        <f>G12+4</f>
+        <f t="shared" si="5"/>
         <v>47952</v>
       </c>
     </row>
@@ -6483,27 +6512,27 @@
         <v>12</v>
       </c>
       <c r="B14" s="9">
-        <f>B13+1</f>
+        <f t="shared" si="2"/>
         <v>47585</v>
       </c>
       <c r="C14" s="9">
-        <f>B14+1</f>
+        <f t="shared" si="0"/>
         <v>47586</v>
       </c>
       <c r="D14" s="9">
-        <f>D13+0.7</f>
+        <f t="shared" si="3"/>
         <v>47703.699999999968</v>
       </c>
       <c r="E14" s="9">
-        <f>D14+0.7</f>
+        <f t="shared" si="1"/>
         <v>47704.399999999965</v>
       </c>
       <c r="F14" s="9">
-        <f>F13+4</f>
+        <f t="shared" si="4"/>
         <v>47952</v>
       </c>
       <c r="G14" s="9">
-        <f>G13+4</f>
+        <f t="shared" si="5"/>
         <v>47956</v>
       </c>
     </row>
@@ -6512,27 +6541,27 @@
         <v>13</v>
       </c>
       <c r="B15" s="9">
-        <f>B14+1</f>
+        <f t="shared" si="2"/>
         <v>47586</v>
       </c>
       <c r="C15" s="9">
-        <f>B15+1</f>
+        <f t="shared" si="0"/>
         <v>47587</v>
       </c>
       <c r="D15" s="9">
-        <f>D14+0.7</f>
+        <f t="shared" si="3"/>
         <v>47704.399999999965</v>
       </c>
       <c r="E15" s="9">
-        <f>D15+0.7</f>
+        <f t="shared" si="1"/>
         <v>47705.099999999962</v>
       </c>
       <c r="F15" s="9">
-        <f>F14+4</f>
+        <f t="shared" si="4"/>
         <v>47956</v>
       </c>
       <c r="G15" s="9">
-        <f>G14+4</f>
+        <f t="shared" si="5"/>
         <v>47960</v>
       </c>
     </row>
@@ -6541,27 +6570,27 @@
         <v>14</v>
       </c>
       <c r="B16" s="9">
-        <f>B15+1</f>
+        <f t="shared" si="2"/>
         <v>47587</v>
       </c>
       <c r="C16" s="9">
-        <f>B16+1</f>
+        <f t="shared" si="0"/>
         <v>47588</v>
       </c>
       <c r="D16" s="9">
-        <f>D15+0.7</f>
+        <f t="shared" si="3"/>
         <v>47705.099999999962</v>
       </c>
       <c r="E16" s="9">
-        <f>D16+0.7</f>
+        <f t="shared" si="1"/>
         <v>47705.799999999959</v>
       </c>
       <c r="F16" s="9">
-        <f>F15+4</f>
+        <f t="shared" si="4"/>
         <v>47960</v>
       </c>
       <c r="G16" s="9">
-        <f>G15+4</f>
+        <f t="shared" si="5"/>
         <v>47964</v>
       </c>
     </row>
@@ -6570,27 +6599,27 @@
         <v>15</v>
       </c>
       <c r="B17" s="9">
-        <f>B16+1</f>
+        <f t="shared" si="2"/>
         <v>47588</v>
       </c>
       <c r="C17" s="9">
-        <f>B17+1</f>
+        <f t="shared" si="0"/>
         <v>47589</v>
       </c>
       <c r="D17" s="9">
-        <f>D16+0.7</f>
+        <f t="shared" si="3"/>
         <v>47705.799999999959</v>
       </c>
       <c r="E17" s="9">
-        <f>D17+0.7</f>
+        <f t="shared" si="1"/>
         <v>47706.499999999956</v>
       </c>
       <c r="F17" s="9">
-        <f>F16+4</f>
+        <f t="shared" si="4"/>
         <v>47964</v>
       </c>
       <c r="G17" s="9">
-        <f>G16+4</f>
+        <f t="shared" si="5"/>
         <v>47968</v>
       </c>
     </row>
@@ -6599,27 +6628,27 @@
         <v>16</v>
       </c>
       <c r="B18" s="9">
-        <f>B17+1</f>
+        <f t="shared" si="2"/>
         <v>47589</v>
       </c>
       <c r="C18" s="9">
-        <f>B18+1</f>
+        <f t="shared" si="0"/>
         <v>47590</v>
       </c>
       <c r="D18" s="9">
-        <f>D17+0.7</f>
+        <f t="shared" si="3"/>
         <v>47706.499999999956</v>
       </c>
       <c r="E18" s="9">
-        <f>D18+0.7</f>
+        <f t="shared" si="1"/>
         <v>47707.199999999953</v>
       </c>
       <c r="F18" s="9">
-        <f>F17+4</f>
+        <f t="shared" si="4"/>
         <v>47968</v>
       </c>
       <c r="G18" s="9">
-        <f>G17+4</f>
+        <f t="shared" si="5"/>
         <v>47972</v>
       </c>
     </row>
@@ -6628,27 +6657,27 @@
         <v>17</v>
       </c>
       <c r="B19" s="9">
-        <f>B18+1</f>
+        <f t="shared" si="2"/>
         <v>47590</v>
       </c>
       <c r="C19" s="9">
-        <f>B19+1</f>
+        <f t="shared" si="0"/>
         <v>47591</v>
       </c>
       <c r="D19" s="9">
-        <f>D18+0.7</f>
+        <f t="shared" si="3"/>
         <v>47707.199999999953</v>
       </c>
       <c r="E19" s="9">
-        <f>D19+0.7</f>
+        <f t="shared" si="1"/>
         <v>47707.899999999951</v>
       </c>
       <c r="F19" s="9">
-        <f>F18+4</f>
+        <f t="shared" si="4"/>
         <v>47972</v>
       </c>
       <c r="G19" s="9">
-        <f>G18+4</f>
+        <f t="shared" si="5"/>
         <v>47976</v>
       </c>
     </row>
@@ -6657,27 +6686,27 @@
         <v>18</v>
       </c>
       <c r="B20" s="9">
-        <f>B19+1</f>
+        <f t="shared" si="2"/>
         <v>47591</v>
       </c>
       <c r="C20" s="9">
-        <f>B20+1</f>
+        <f t="shared" si="0"/>
         <v>47592</v>
       </c>
       <c r="D20" s="9">
-        <f>D19+0.7</f>
+        <f t="shared" si="3"/>
         <v>47707.899999999951</v>
       </c>
       <c r="E20" s="9">
-        <f>D20+0.7</f>
+        <f t="shared" si="1"/>
         <v>47708.599999999948</v>
       </c>
       <c r="F20" s="9">
-        <f>F19+4</f>
+        <f t="shared" si="4"/>
         <v>47976</v>
       </c>
       <c r="G20" s="9">
-        <f>G19+4</f>
+        <f t="shared" si="5"/>
         <v>47980</v>
       </c>
     </row>
@@ -6686,27 +6715,27 @@
         <v>19</v>
       </c>
       <c r="B21" s="9">
-        <f>B20+1</f>
+        <f t="shared" si="2"/>
         <v>47592</v>
       </c>
       <c r="C21" s="9">
-        <f>B21+1</f>
+        <f t="shared" si="0"/>
         <v>47593</v>
       </c>
       <c r="D21" s="9">
-        <f>D20+0.7</f>
+        <f t="shared" si="3"/>
         <v>47708.599999999948</v>
       </c>
       <c r="E21" s="9">
-        <f>D21+0.7</f>
+        <f t="shared" si="1"/>
         <v>47709.299999999945</v>
       </c>
       <c r="F21" s="9">
-        <f>F20+4</f>
+        <f t="shared" si="4"/>
         <v>47980</v>
       </c>
       <c r="G21" s="9">
-        <f>G20+4</f>
+        <f t="shared" si="5"/>
         <v>47984</v>
       </c>
     </row>
@@ -6715,27 +6744,27 @@
         <v>20</v>
       </c>
       <c r="B22" s="9">
-        <f>B21+1</f>
+        <f t="shared" si="2"/>
         <v>47593</v>
       </c>
       <c r="C22" s="9">
-        <f>B22+1</f>
+        <f t="shared" si="0"/>
         <v>47594</v>
       </c>
       <c r="D22" s="9">
-        <f>D21+0.7</f>
+        <f t="shared" si="3"/>
         <v>47709.299999999945</v>
       </c>
       <c r="E22" s="9">
-        <f>D22+0.7</f>
+        <f t="shared" si="1"/>
         <v>47709.999999999942</v>
       </c>
       <c r="F22" s="9">
-        <f>F21+4</f>
+        <f t="shared" si="4"/>
         <v>47984</v>
       </c>
       <c r="G22" s="9">
-        <f>G21+4</f>
+        <f t="shared" si="5"/>
         <v>47988</v>
       </c>
     </row>
@@ -6744,27 +6773,27 @@
         <v>21</v>
       </c>
       <c r="B23" s="9">
-        <f>B22+1</f>
+        <f t="shared" si="2"/>
         <v>47594</v>
       </c>
       <c r="C23" s="9">
-        <f>B23+1</f>
+        <f t="shared" si="0"/>
         <v>47595</v>
       </c>
       <c r="D23" s="9">
-        <f>D22+0.7</f>
+        <f t="shared" si="3"/>
         <v>47709.999999999942</v>
       </c>
       <c r="E23" s="9">
-        <f>D23+0.7</f>
+        <f t="shared" si="1"/>
         <v>47710.699999999939</v>
       </c>
       <c r="F23" s="9">
-        <f>F22+4</f>
+        <f t="shared" si="4"/>
         <v>47988</v>
       </c>
       <c r="G23" s="9">
-        <f>G22+4</f>
+        <f t="shared" si="5"/>
         <v>47992</v>
       </c>
     </row>
@@ -6773,27 +6802,27 @@
         <v>22</v>
       </c>
       <c r="B24" s="9">
-        <f>B23+1</f>
+        <f t="shared" si="2"/>
         <v>47595</v>
       </c>
       <c r="C24" s="9">
-        <f>B24+1</f>
+        <f t="shared" si="0"/>
         <v>47596</v>
       </c>
       <c r="D24" s="9">
-        <f>D23+0.7</f>
+        <f t="shared" si="3"/>
         <v>47710.699999999939</v>
       </c>
       <c r="E24" s="9">
-        <f>D24+0.7</f>
+        <f t="shared" si="1"/>
         <v>47711.399999999936</v>
       </c>
       <c r="F24" s="9">
-        <f>F23+4</f>
+        <f t="shared" si="4"/>
         <v>47992</v>
       </c>
       <c r="G24" s="9">
-        <f>G23+4</f>
+        <f t="shared" si="5"/>
         <v>47996</v>
       </c>
     </row>
@@ -6802,27 +6831,27 @@
         <v>23</v>
       </c>
       <c r="B25" s="9">
-        <f>B24+1</f>
+        <f t="shared" si="2"/>
         <v>47596</v>
       </c>
       <c r="C25" s="9">
-        <f>B25+1</f>
+        <f t="shared" si="0"/>
         <v>47597</v>
       </c>
       <c r="D25" s="9">
-        <f>D24+0.7</f>
+        <f t="shared" si="3"/>
         <v>47711.399999999936</v>
       </c>
       <c r="E25" s="9">
-        <f>D25+0.7</f>
+        <f t="shared" si="1"/>
         <v>47712.099999999933</v>
       </c>
       <c r="F25" s="9">
-        <f>F24+4</f>
+        <f t="shared" si="4"/>
         <v>47996</v>
       </c>
       <c r="G25" s="9">
-        <f>G24+4</f>
+        <f t="shared" si="5"/>
         <v>48000</v>
       </c>
     </row>
@@ -6831,27 +6860,27 @@
         <v>24</v>
       </c>
       <c r="B26" s="9">
-        <f>B25+1</f>
+        <f t="shared" si="2"/>
         <v>47597</v>
       </c>
       <c r="C26" s="9">
-        <f>B26+1</f>
+        <f t="shared" si="0"/>
         <v>47598</v>
       </c>
       <c r="D26" s="9">
-        <f>D25+0.7</f>
+        <f t="shared" si="3"/>
         <v>47712.099999999933</v>
       </c>
       <c r="E26" s="9">
-        <f>D26+0.7</f>
+        <f t="shared" si="1"/>
         <v>47712.79999999993</v>
       </c>
       <c r="F26" s="9">
-        <f>F25+4</f>
+        <f t="shared" si="4"/>
         <v>48000</v>
       </c>
       <c r="G26" s="9">
-        <f>G25+4</f>
+        <f t="shared" si="5"/>
         <v>48004</v>
       </c>
     </row>
@@ -6860,27 +6889,27 @@
         <v>25</v>
       </c>
       <c r="B27" s="9">
-        <f>B26+1</f>
+        <f t="shared" si="2"/>
         <v>47598</v>
       </c>
       <c r="C27" s="9">
-        <f>B27+1</f>
+        <f t="shared" si="0"/>
         <v>47599</v>
       </c>
       <c r="D27" s="9">
-        <f>D26+0.7</f>
+        <f t="shared" si="3"/>
         <v>47712.79999999993</v>
       </c>
       <c r="E27" s="9">
-        <f>D27+0.7</f>
+        <f t="shared" si="1"/>
         <v>47713.499999999927</v>
       </c>
       <c r="F27" s="9">
-        <f>F26+4</f>
+        <f t="shared" si="4"/>
         <v>48004</v>
       </c>
       <c r="G27" s="9">
-        <f>G26+4</f>
+        <f t="shared" si="5"/>
         <v>48008</v>
       </c>
     </row>
@@ -6889,27 +6918,27 @@
         <v>26</v>
       </c>
       <c r="B28" s="9">
-        <f>B27+1</f>
+        <f t="shared" si="2"/>
         <v>47599</v>
       </c>
       <c r="C28" s="9">
-        <f>B28+1</f>
+        <f t="shared" si="0"/>
         <v>47600</v>
       </c>
       <c r="D28" s="9">
-        <f>D27+0.7</f>
+        <f t="shared" si="3"/>
         <v>47713.499999999927</v>
       </c>
       <c r="E28" s="9">
-        <f>D28+0.7</f>
+        <f t="shared" si="1"/>
         <v>47714.199999999924</v>
       </c>
       <c r="F28" s="9">
-        <f>F27+4</f>
+        <f t="shared" si="4"/>
         <v>48008</v>
       </c>
       <c r="G28" s="9">
-        <f>G27+4</f>
+        <f t="shared" si="5"/>
         <v>48012</v>
       </c>
     </row>
@@ -6918,27 +6947,27 @@
         <v>27</v>
       </c>
       <c r="B29" s="9">
-        <f>B28+1</f>
+        <f t="shared" si="2"/>
         <v>47600</v>
       </c>
       <c r="C29" s="9">
-        <f>B29+1</f>
+        <f t="shared" si="0"/>
         <v>47601</v>
       </c>
       <c r="D29" s="9">
-        <f>D28+0.7</f>
+        <f t="shared" si="3"/>
         <v>47714.199999999924</v>
       </c>
       <c r="E29" s="9">
-        <f>D29+0.7</f>
+        <f t="shared" si="1"/>
         <v>47714.899999999921</v>
       </c>
       <c r="F29" s="9">
-        <f>F28+4</f>
+        <f t="shared" si="4"/>
         <v>48012</v>
       </c>
       <c r="G29" s="9">
-        <f>G28+4</f>
+        <f t="shared" si="5"/>
         <v>48016</v>
       </c>
     </row>
@@ -6947,27 +6976,27 @@
         <v>28</v>
       </c>
       <c r="B30" s="9">
-        <f>B29+1</f>
+        <f t="shared" si="2"/>
         <v>47601</v>
       </c>
       <c r="C30" s="9">
-        <f>B30+1</f>
+        <f t="shared" si="0"/>
         <v>47602</v>
       </c>
       <c r="D30" s="9">
-        <f>D29+0.7</f>
+        <f t="shared" si="3"/>
         <v>47714.899999999921</v>
       </c>
       <c r="E30" s="9">
-        <f>D30+0.7</f>
+        <f t="shared" si="1"/>
         <v>47715.599999999919</v>
       </c>
       <c r="F30" s="9">
-        <f>F29+4</f>
+        <f t="shared" si="4"/>
         <v>48016</v>
       </c>
       <c r="G30" s="9">
-        <f>G29+4</f>
+        <f t="shared" si="5"/>
         <v>48020</v>
       </c>
     </row>
@@ -6976,27 +7005,27 @@
         <v>29</v>
       </c>
       <c r="B31" s="9">
-        <f>B30+1</f>
+        <f t="shared" si="2"/>
         <v>47602</v>
       </c>
       <c r="C31" s="9">
-        <f>B31+1</f>
+        <f t="shared" si="0"/>
         <v>47603</v>
       </c>
       <c r="D31" s="9">
-        <f>D30+0.7</f>
+        <f t="shared" si="3"/>
         <v>47715.599999999919</v>
       </c>
       <c r="E31" s="9">
-        <f>D31+0.7</f>
+        <f t="shared" si="1"/>
         <v>47716.299999999916</v>
       </c>
       <c r="F31" s="9">
-        <f>F30+4</f>
+        <f t="shared" si="4"/>
         <v>48020</v>
       </c>
       <c r="G31" s="9">
-        <f>G30+4</f>
+        <f t="shared" si="5"/>
         <v>48024</v>
       </c>
     </row>
@@ -7005,27 +7034,27 @@
         <v>30</v>
       </c>
       <c r="B32" s="9">
-        <f>B31+1</f>
+        <f t="shared" si="2"/>
         <v>47603</v>
       </c>
       <c r="C32" s="9">
-        <f>B32+1</f>
+        <f t="shared" si="0"/>
         <v>47604</v>
       </c>
       <c r="D32" s="9">
-        <f>D31+0.7</f>
+        <f t="shared" si="3"/>
         <v>47716.299999999916</v>
       </c>
       <c r="E32" s="9">
-        <f>D32+0.7</f>
+        <f t="shared" si="1"/>
         <v>47716.999999999913</v>
       </c>
       <c r="F32" s="9">
-        <f>F31+4</f>
+        <f t="shared" si="4"/>
         <v>48024</v>
       </c>
       <c r="G32" s="9">
-        <f>G31+4</f>
+        <f t="shared" si="5"/>
         <v>48028</v>
       </c>
     </row>
@@ -7034,27 +7063,27 @@
         <v>31</v>
       </c>
       <c r="B33" s="9">
-        <f>B32+1</f>
+        <f t="shared" si="2"/>
         <v>47604</v>
       </c>
       <c r="C33" s="9">
-        <f>B33+1</f>
+        <f t="shared" si="0"/>
         <v>47605</v>
       </c>
       <c r="D33" s="9">
-        <f>D32+0.7</f>
+        <f t="shared" si="3"/>
         <v>47716.999999999913</v>
       </c>
       <c r="E33" s="9">
-        <f>D33+0.7</f>
+        <f t="shared" si="1"/>
         <v>47717.69999999991</v>
       </c>
       <c r="F33" s="9">
-        <f>F32+4</f>
+        <f t="shared" si="4"/>
         <v>48028</v>
       </c>
       <c r="G33" s="9">
-        <f>G32+4</f>
+        <f t="shared" si="5"/>
         <v>48032</v>
       </c>
     </row>
@@ -7063,27 +7092,27 @@
         <v>32</v>
       </c>
       <c r="B34" s="9">
-        <f>B33+1</f>
+        <f t="shared" si="2"/>
         <v>47605</v>
       </c>
       <c r="C34" s="9">
-        <f>B34+1</f>
+        <f t="shared" si="0"/>
         <v>47606</v>
       </c>
       <c r="D34" s="9">
-        <f>D33+0.7</f>
+        <f t="shared" si="3"/>
         <v>47717.69999999991</v>
       </c>
       <c r="E34" s="9">
-        <f>D34+0.7</f>
+        <f t="shared" si="1"/>
         <v>47718.399999999907</v>
       </c>
       <c r="F34" s="9">
-        <f>F33+4</f>
+        <f t="shared" si="4"/>
         <v>48032</v>
       </c>
       <c r="G34" s="9">
-        <f>G33+4</f>
+        <f t="shared" si="5"/>
         <v>48036</v>
       </c>
     </row>
@@ -7092,27 +7121,27 @@
         <v>33</v>
       </c>
       <c r="B35" s="9">
-        <f>B34+1</f>
+        <f t="shared" si="2"/>
         <v>47606</v>
       </c>
       <c r="C35" s="9">
-        <f>B35+1</f>
+        <f t="shared" ref="C35:C66" si="6">B35+1</f>
         <v>47607</v>
       </c>
       <c r="D35" s="9">
-        <f>D34+0.7</f>
+        <f t="shared" si="3"/>
         <v>47718.399999999907</v>
       </c>
       <c r="E35" s="9">
-        <f>D35+0.7</f>
+        <f t="shared" ref="E35:E66" si="7">D35+0.7</f>
         <v>47719.099999999904</v>
       </c>
       <c r="F35" s="9">
-        <f>F34+4</f>
+        <f t="shared" si="4"/>
         <v>48036</v>
       </c>
       <c r="G35" s="9">
-        <f>G34+4</f>
+        <f t="shared" si="5"/>
         <v>48040</v>
       </c>
     </row>
@@ -7121,27 +7150,27 @@
         <v>34</v>
       </c>
       <c r="B36" s="9">
-        <f>B35+1</f>
+        <f t="shared" ref="B36:B52" si="8">B35+1</f>
         <v>47607</v>
       </c>
       <c r="C36" s="9">
-        <f>B36+1</f>
+        <f t="shared" si="6"/>
         <v>47608</v>
       </c>
       <c r="D36" s="9">
-        <f>D35+0.7</f>
+        <f t="shared" ref="D36:D57" si="9">D35+0.7</f>
         <v>47719.099999999904</v>
       </c>
       <c r="E36" s="9">
-        <f>D36+0.7</f>
+        <f t="shared" si="7"/>
         <v>47719.799999999901</v>
       </c>
       <c r="F36" s="9">
-        <f>F35+4</f>
+        <f t="shared" ref="F36:F52" si="10">F35+4</f>
         <v>48040</v>
       </c>
       <c r="G36" s="9">
-        <f>G35+4</f>
+        <f t="shared" ref="G36:G52" si="11">G35+4</f>
         <v>48044</v>
       </c>
     </row>
@@ -7150,27 +7179,27 @@
         <v>35</v>
       </c>
       <c r="B37" s="9">
-        <f>B36+1</f>
+        <f t="shared" si="8"/>
         <v>47608</v>
       </c>
       <c r="C37" s="9">
-        <f>B37+1</f>
+        <f t="shared" si="6"/>
         <v>47609</v>
       </c>
       <c r="D37" s="9">
-        <f>D36+0.7</f>
+        <f t="shared" si="9"/>
         <v>47719.799999999901</v>
       </c>
       <c r="E37" s="9">
-        <f>D37+0.7</f>
+        <f t="shared" si="7"/>
         <v>47720.499999999898</v>
       </c>
       <c r="F37" s="9">
-        <f>F36+4</f>
+        <f t="shared" si="10"/>
         <v>48044</v>
       </c>
       <c r="G37" s="9">
-        <f>G36+4</f>
+        <f t="shared" si="11"/>
         <v>48048</v>
       </c>
     </row>
@@ -7179,27 +7208,27 @@
         <v>36</v>
       </c>
       <c r="B38" s="9">
-        <f>B37+1</f>
+        <f t="shared" si="8"/>
         <v>47609</v>
       </c>
       <c r="C38" s="9">
-        <f>B38+1</f>
+        <f t="shared" si="6"/>
         <v>47610</v>
       </c>
       <c r="D38" s="9">
-        <f>D37+0.7</f>
+        <f t="shared" si="9"/>
         <v>47720.499999999898</v>
       </c>
       <c r="E38" s="9">
-        <f>D38+0.7</f>
+        <f t="shared" si="7"/>
         <v>47721.199999999895</v>
       </c>
       <c r="F38" s="9">
-        <f>F37+4</f>
+        <f t="shared" si="10"/>
         <v>48048</v>
       </c>
       <c r="G38" s="9">
-        <f>G37+4</f>
+        <f t="shared" si="11"/>
         <v>48052</v>
       </c>
     </row>
@@ -7208,27 +7237,27 @@
         <v>37</v>
       </c>
       <c r="B39" s="9">
-        <f>B38+1</f>
+        <f t="shared" si="8"/>
         <v>47610</v>
       </c>
       <c r="C39" s="9">
-        <f>B39+1</f>
+        <f t="shared" si="6"/>
         <v>47611</v>
       </c>
       <c r="D39" s="9">
-        <f>D38+0.7</f>
+        <f t="shared" si="9"/>
         <v>47721.199999999895</v>
       </c>
       <c r="E39" s="9">
-        <f>D39+0.7</f>
+        <f t="shared" si="7"/>
         <v>47721.899999999892</v>
       </c>
       <c r="F39" s="9">
-        <f>F38+4</f>
+        <f t="shared" si="10"/>
         <v>48052</v>
       </c>
       <c r="G39" s="9">
-        <f>G38+4</f>
+        <f t="shared" si="11"/>
         <v>48056</v>
       </c>
     </row>
@@ -7237,27 +7266,27 @@
         <v>38</v>
       </c>
       <c r="B40" s="9">
-        <f>B39+1</f>
+        <f t="shared" si="8"/>
         <v>47611</v>
       </c>
       <c r="C40" s="9">
-        <f>B40+1</f>
+        <f t="shared" si="6"/>
         <v>47612</v>
       </c>
       <c r="D40" s="9">
-        <f>D39+0.7</f>
+        <f t="shared" si="9"/>
         <v>47721.899999999892</v>
       </c>
       <c r="E40" s="9">
-        <f>D40+0.7</f>
+        <f t="shared" si="7"/>
         <v>47722.599999999889</v>
       </c>
       <c r="F40" s="9">
-        <f>F39+4</f>
+        <f t="shared" si="10"/>
         <v>48056</v>
       </c>
       <c r="G40" s="9">
-        <f>G39+4</f>
+        <f t="shared" si="11"/>
         <v>48060</v>
       </c>
     </row>
@@ -7266,27 +7295,27 @@
         <v>39</v>
       </c>
       <c r="B41" s="9">
-        <f>B40+1</f>
+        <f t="shared" si="8"/>
         <v>47612</v>
       </c>
       <c r="C41" s="9">
-        <f>B41+1</f>
+        <f t="shared" si="6"/>
         <v>47613</v>
       </c>
       <c r="D41" s="9">
-        <f>D40+0.7</f>
+        <f t="shared" si="9"/>
         <v>47722.599999999889</v>
       </c>
       <c r="E41" s="9">
-        <f>D41+0.7</f>
+        <f t="shared" si="7"/>
         <v>47723.299999999886</v>
       </c>
       <c r="F41" s="9">
-        <f>F40+4</f>
+        <f t="shared" si="10"/>
         <v>48060</v>
       </c>
       <c r="G41" s="9">
-        <f>G40+4</f>
+        <f t="shared" si="11"/>
         <v>48064</v>
       </c>
     </row>
@@ -7295,27 +7324,27 @@
         <v>40</v>
       </c>
       <c r="B42" s="9">
-        <f>B41+1</f>
+        <f t="shared" si="8"/>
         <v>47613</v>
       </c>
       <c r="C42" s="9">
-        <f>B42+1</f>
+        <f t="shared" si="6"/>
         <v>47614</v>
       </c>
       <c r="D42" s="9">
-        <f>D41+0.7</f>
+        <f t="shared" si="9"/>
         <v>47723.299999999886</v>
       </c>
       <c r="E42" s="9">
-        <f>D42+0.7</f>
+        <f t="shared" si="7"/>
         <v>47723.999999999884</v>
       </c>
       <c r="F42" s="9">
-        <f>F41+4</f>
+        <f t="shared" si="10"/>
         <v>48064</v>
       </c>
       <c r="G42" s="9">
-        <f>G41+4</f>
+        <f t="shared" si="11"/>
         <v>48068</v>
       </c>
     </row>
@@ -7324,27 +7353,27 @@
         <v>41</v>
       </c>
       <c r="B43" s="9">
-        <f>B42+1</f>
+        <f t="shared" si="8"/>
         <v>47614</v>
       </c>
       <c r="C43" s="9">
-        <f>B43+1</f>
+        <f t="shared" si="6"/>
         <v>47615</v>
       </c>
       <c r="D43" s="9">
-        <f>D42+0.7</f>
+        <f t="shared" si="9"/>
         <v>47723.999999999884</v>
       </c>
       <c r="E43" s="9">
-        <f>D43+0.7</f>
+        <f t="shared" si="7"/>
         <v>47724.699999999881</v>
       </c>
       <c r="F43" s="9">
-        <f>F42+4</f>
+        <f t="shared" si="10"/>
         <v>48068</v>
       </c>
       <c r="G43" s="9">
-        <f>G42+4</f>
+        <f t="shared" si="11"/>
         <v>48072</v>
       </c>
     </row>
@@ -7353,27 +7382,27 @@
         <v>42</v>
       </c>
       <c r="B44" s="9">
-        <f>B43+1</f>
+        <f t="shared" si="8"/>
         <v>47615</v>
       </c>
       <c r="C44" s="9">
-        <f>B44+1</f>
+        <f t="shared" si="6"/>
         <v>47616</v>
       </c>
       <c r="D44" s="9">
-        <f>D43+0.7</f>
+        <f t="shared" si="9"/>
         <v>47724.699999999881</v>
       </c>
       <c r="E44" s="9">
-        <f>D44+0.7</f>
+        <f t="shared" si="7"/>
         <v>47725.399999999878</v>
       </c>
       <c r="F44" s="9">
-        <f>F43+4</f>
+        <f t="shared" si="10"/>
         <v>48072</v>
       </c>
       <c r="G44" s="9">
-        <f>G43+4</f>
+        <f t="shared" si="11"/>
         <v>48076</v>
       </c>
     </row>
@@ -7382,27 +7411,27 @@
         <v>43</v>
       </c>
       <c r="B45" s="9">
-        <f>B44+1</f>
+        <f t="shared" si="8"/>
         <v>47616</v>
       </c>
       <c r="C45" s="9">
-        <f>B45+1</f>
+        <f t="shared" si="6"/>
         <v>47617</v>
       </c>
       <c r="D45" s="9">
-        <f>D44+0.7</f>
+        <f t="shared" si="9"/>
         <v>47725.399999999878</v>
       </c>
       <c r="E45" s="9">
-        <f>D45+0.7</f>
+        <f t="shared" si="7"/>
         <v>47726.099999999875</v>
       </c>
       <c r="F45" s="9">
-        <f>F44+4</f>
+        <f t="shared" si="10"/>
         <v>48076</v>
       </c>
       <c r="G45" s="9">
-        <f>G44+4</f>
+        <f t="shared" si="11"/>
         <v>48080</v>
       </c>
     </row>
@@ -7411,27 +7440,27 @@
         <v>44</v>
       </c>
       <c r="B46" s="9">
-        <f>B45+1</f>
+        <f t="shared" si="8"/>
         <v>47617</v>
       </c>
       <c r="C46" s="9">
-        <f>B46+1</f>
+        <f t="shared" si="6"/>
         <v>47618</v>
       </c>
       <c r="D46" s="9">
-        <f>D45+0.7</f>
+        <f t="shared" si="9"/>
         <v>47726.099999999875</v>
       </c>
       <c r="E46" s="9">
-        <f>D46+0.7</f>
+        <f t="shared" si="7"/>
         <v>47726.799999999872</v>
       </c>
       <c r="F46" s="9">
-        <f>F45+4</f>
+        <f t="shared" si="10"/>
         <v>48080</v>
       </c>
       <c r="G46" s="9">
-        <f>G45+4</f>
+        <f t="shared" si="11"/>
         <v>48084</v>
       </c>
     </row>
@@ -7440,27 +7469,27 @@
         <v>45</v>
       </c>
       <c r="B47" s="9">
-        <f>B46+1</f>
+        <f t="shared" si="8"/>
         <v>47618</v>
       </c>
       <c r="C47" s="9">
-        <f>B47+1</f>
+        <f t="shared" si="6"/>
         <v>47619</v>
       </c>
       <c r="D47" s="9">
-        <f>D46+0.7</f>
+        <f t="shared" si="9"/>
         <v>47726.799999999872</v>
       </c>
       <c r="E47" s="9">
-        <f>D47+0.7</f>
+        <f t="shared" si="7"/>
         <v>47727.499999999869</v>
       </c>
       <c r="F47" s="9">
-        <f>F46+4</f>
+        <f t="shared" si="10"/>
         <v>48084</v>
       </c>
       <c r="G47" s="9">
-        <f>G46+4</f>
+        <f t="shared" si="11"/>
         <v>48088</v>
       </c>
     </row>
@@ -7469,27 +7498,27 @@
         <v>46</v>
       </c>
       <c r="B48" s="9">
-        <f>B47+1</f>
+        <f t="shared" si="8"/>
         <v>47619</v>
       </c>
       <c r="C48" s="9">
-        <f>B48+1</f>
+        <f t="shared" si="6"/>
         <v>47620</v>
       </c>
       <c r="D48" s="9">
-        <f>D47+0.7</f>
+        <f t="shared" si="9"/>
         <v>47727.499999999869</v>
       </c>
       <c r="E48" s="9">
-        <f>D48+0.7</f>
+        <f t="shared" si="7"/>
         <v>47728.199999999866</v>
       </c>
       <c r="F48" s="9">
-        <f>F47+4</f>
+        <f t="shared" si="10"/>
         <v>48088</v>
       </c>
       <c r="G48" s="9">
-        <f>G47+4</f>
+        <f t="shared" si="11"/>
         <v>48092</v>
       </c>
     </row>
@@ -7498,27 +7527,27 @@
         <v>47</v>
       </c>
       <c r="B49" s="9">
-        <f>B48+1</f>
+        <f t="shared" si="8"/>
         <v>47620</v>
       </c>
       <c r="C49" s="9">
-        <f>B49+1</f>
+        <f t="shared" si="6"/>
         <v>47621</v>
       </c>
       <c r="D49" s="9">
-        <f>D48+0.7</f>
+        <f t="shared" si="9"/>
         <v>47728.199999999866</v>
       </c>
       <c r="E49" s="9">
-        <f>D49+0.7</f>
+        <f t="shared" si="7"/>
         <v>47728.899999999863</v>
       </c>
       <c r="F49" s="9">
-        <f>F48+4</f>
+        <f t="shared" si="10"/>
         <v>48092</v>
       </c>
       <c r="G49" s="9">
-        <f>G48+4</f>
+        <f t="shared" si="11"/>
         <v>48096</v>
       </c>
     </row>
@@ -7527,27 +7556,27 @@
         <v>48</v>
       </c>
       <c r="B50" s="9">
-        <f>B49+1</f>
+        <f t="shared" si="8"/>
         <v>47621</v>
       </c>
       <c r="C50" s="9">
-        <f>B50+1</f>
+        <f t="shared" si="6"/>
         <v>47622</v>
       </c>
       <c r="D50" s="9">
-        <f>D49+0.7</f>
+        <f t="shared" si="9"/>
         <v>47728.899999999863</v>
       </c>
       <c r="E50" s="9">
-        <f>D50+0.7</f>
+        <f t="shared" si="7"/>
         <v>47729.59999999986</v>
       </c>
       <c r="F50" s="9">
-        <f>F49+4</f>
+        <f t="shared" si="10"/>
         <v>48096</v>
       </c>
       <c r="G50" s="9">
-        <f>G49+4</f>
+        <f t="shared" si="11"/>
         <v>48100</v>
       </c>
     </row>
@@ -7556,27 +7585,27 @@
         <v>49</v>
       </c>
       <c r="B51" s="9">
-        <f>B50+1</f>
+        <f t="shared" si="8"/>
         <v>47622</v>
       </c>
       <c r="C51" s="9">
-        <f>B51+1</f>
+        <f t="shared" si="6"/>
         <v>47623</v>
       </c>
       <c r="D51" s="9">
-        <f>D50+0.7</f>
+        <f t="shared" si="9"/>
         <v>47729.59999999986</v>
       </c>
       <c r="E51" s="9">
-        <f>D51+0.7</f>
+        <f t="shared" si="7"/>
         <v>47730.299999999857</v>
       </c>
       <c r="F51" s="9">
-        <f>F50+4</f>
+        <f t="shared" si="10"/>
         <v>48100</v>
       </c>
       <c r="G51" s="9">
-        <f>G50+4</f>
+        <f t="shared" si="11"/>
         <v>48104</v>
       </c>
     </row>
@@ -7585,27 +7614,27 @@
         <v>50</v>
       </c>
       <c r="B52" s="9">
-        <f>B51+1</f>
+        <f t="shared" si="8"/>
         <v>47623</v>
       </c>
       <c r="C52" s="9">
-        <f>B52+1</f>
+        <f t="shared" si="6"/>
         <v>47624</v>
       </c>
       <c r="D52" s="9">
-        <f>D51+0.7</f>
+        <f t="shared" si="9"/>
         <v>47730.299999999857</v>
       </c>
       <c r="E52" s="9">
-        <f>D52+0.7</f>
+        <f t="shared" si="7"/>
         <v>47730.999999999854</v>
       </c>
       <c r="F52" s="9">
-        <f>F51+4</f>
+        <f t="shared" si="10"/>
         <v>48104</v>
       </c>
       <c r="G52" s="9">
-        <f>G51+4</f>
+        <f t="shared" si="11"/>
         <v>48108</v>
       </c>
     </row>
@@ -7616,11 +7645,11 @@
       <c r="B53" s="23"/>
       <c r="C53" s="23"/>
       <c r="D53" s="9">
-        <f>D52+0.7</f>
+        <f t="shared" si="9"/>
         <v>47730.999999999854</v>
       </c>
       <c r="E53" s="9">
-        <f>D53+0.7</f>
+        <f t="shared" si="7"/>
         <v>47731.699999999852</v>
       </c>
       <c r="F53" s="23"/>
@@ -7633,11 +7662,11 @@
       <c r="B54" s="23"/>
       <c r="C54" s="23"/>
       <c r="D54" s="9">
-        <f>D53+0.7</f>
+        <f t="shared" si="9"/>
         <v>47731.699999999852</v>
       </c>
       <c r="E54" s="9">
-        <f>D54+0.7</f>
+        <f t="shared" si="7"/>
         <v>47732.399999999849</v>
       </c>
       <c r="F54" s="23"/>
@@ -7650,11 +7679,11 @@
       <c r="B55" s="23"/>
       <c r="C55" s="23"/>
       <c r="D55" s="9">
-        <f>D54+0.7</f>
+        <f t="shared" si="9"/>
         <v>47732.399999999849</v>
       </c>
       <c r="E55" s="9">
-        <f>D55+0.7</f>
+        <f t="shared" si="7"/>
         <v>47733.099999999846</v>
       </c>
       <c r="F55" s="23"/>
@@ -7667,11 +7696,11 @@
       <c r="B56" s="23"/>
       <c r="C56" s="23"/>
       <c r="D56" s="9">
-        <f>D55+0.7</f>
+        <f t="shared" si="9"/>
         <v>47733.099999999846</v>
       </c>
       <c r="E56" s="9">
-        <f>D56+0.7</f>
+        <f t="shared" si="7"/>
         <v>47733.799999999843</v>
       </c>
       <c r="F56" s="23"/>
@@ -7684,11 +7713,11 @@
       <c r="B57" s="23"/>
       <c r="C57" s="23"/>
       <c r="D57" s="9">
-        <f>D56+0.7</f>
+        <f t="shared" si="9"/>
         <v>47733.799999999843</v>
       </c>
       <c r="E57" s="9">
-        <f>D57+0.7</f>
+        <f t="shared" si="7"/>
         <v>47734.49999999984</v>
       </c>
       <c r="F57" s="23"/>
@@ -8015,15 +8044,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <Revised xmlns="7b1e1d97-de89-451e-b61e-3a612707828f">false</Revised>
@@ -8038,6 +8058,15 @@
     <OEM xmlns="7b1e1d97-de89-451e-b61e-3a612707828f" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8062,14 +8091,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D87E93EE-9EE0-4F81-BCAE-80D6FC49D1B7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EBE4A505-FD97-4F62-A54E-794D67C3C89E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="7b1e1d97-de89-451e-b61e-3a612707828f"/>
@@ -8088,6 +8109,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D87E93EE-9EE0-4F81-BCAE-80D6FC49D1B7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{f481d56f-c63d-4d74-8406-d64e74f44395}" enabled="0" method="" siteId="{f481d56f-c63d-4d74-8406-d64e74f44395}" removed="1"/>

--- a/sequencer input v2.xlsx
+++ b/sequencer input v2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ui208936\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C7FA2A1-877B-4365-A6AD-EAE742E01576}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2572DBD2-741D-4E8D-A10C-61986A833646}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-67320" yWindow="-3525" windowWidth="29040" windowHeight="15720" xr2:uid="{45D2DF17-6F7C-45FD-9E14-08090A3A3102}"/>
+    <workbookView xWindow="-30828" yWindow="-2832" windowWidth="30936" windowHeight="16776" xr2:uid="{45D2DF17-6F7C-45FD-9E14-08090A3A3102}"/>
   </bookViews>
   <sheets>
     <sheet name="FOU data" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'FOU data'!$A$1:$N$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'IAC data'!$A$1:$H$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'WTG data'!$A$1:$H$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'WTG data'!$A$1:$F$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="976" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="874" uniqueCount="152">
   <si>
     <t>Structure</t>
   </si>
@@ -230,159 +230,6 @@
   </si>
   <si>
     <t>IAC</t>
-  </si>
-  <si>
-    <t>S1_01</t>
-  </si>
-  <si>
-    <t>S1_02</t>
-  </si>
-  <si>
-    <t>S1_03</t>
-  </si>
-  <si>
-    <t>S1_04</t>
-  </si>
-  <si>
-    <t>S1_05</t>
-  </si>
-  <si>
-    <t>S2_01</t>
-  </si>
-  <si>
-    <t>S2_02</t>
-  </si>
-  <si>
-    <t>S2_03</t>
-  </si>
-  <si>
-    <t>S2_04</t>
-  </si>
-  <si>
-    <t>S2_05</t>
-  </si>
-  <si>
-    <t>S3_01</t>
-  </si>
-  <si>
-    <t>S3_02</t>
-  </si>
-  <si>
-    <t>S3_03</t>
-  </si>
-  <si>
-    <t>S3_04</t>
-  </si>
-  <si>
-    <t>S3_05</t>
-  </si>
-  <si>
-    <t>S4_01</t>
-  </si>
-  <si>
-    <t>S4_02</t>
-  </si>
-  <si>
-    <t>S4_03</t>
-  </si>
-  <si>
-    <t>S4_04</t>
-  </si>
-  <si>
-    <t>S4_05</t>
-  </si>
-  <si>
-    <t>S5_01</t>
-  </si>
-  <si>
-    <t>S5_02</t>
-  </si>
-  <si>
-    <t>S5_03</t>
-  </si>
-  <si>
-    <t>S5_04</t>
-  </si>
-  <si>
-    <t>S5_05</t>
-  </si>
-  <si>
-    <t>S6_01</t>
-  </si>
-  <si>
-    <t>S6_02</t>
-  </si>
-  <si>
-    <t>S6_03</t>
-  </si>
-  <si>
-    <t>S6_04</t>
-  </si>
-  <si>
-    <t>S6_05</t>
-  </si>
-  <si>
-    <t>S7_01</t>
-  </si>
-  <si>
-    <t>S7_02</t>
-  </si>
-  <si>
-    <t>S7_03</t>
-  </si>
-  <si>
-    <t>S7_04</t>
-  </si>
-  <si>
-    <t>S7_05</t>
-  </si>
-  <si>
-    <t>S8_01</t>
-  </si>
-  <si>
-    <t>S8_02</t>
-  </si>
-  <si>
-    <t>S8_03</t>
-  </si>
-  <si>
-    <t>S8_04</t>
-  </si>
-  <si>
-    <t>S8_05</t>
-  </si>
-  <si>
-    <t>S9_01</t>
-  </si>
-  <si>
-    <t>S9_02</t>
-  </si>
-  <si>
-    <t>S9_03</t>
-  </si>
-  <si>
-    <t>S9_04</t>
-  </si>
-  <si>
-    <t>S9_05</t>
-  </si>
-  <si>
-    <t>S10_01</t>
-  </si>
-  <si>
-    <t>S10_02</t>
-  </si>
-  <si>
-    <t>S10_03</t>
-  </si>
-  <si>
-    <t>S10_04</t>
-  </si>
-  <si>
-    <t>S10_05</t>
-  </si>
-  <si>
-    <t>String</t>
   </si>
   <si>
     <t xml:space="preserve">Easy </t>
@@ -1049,7 +896,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1165,45 +1012,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1561,7 +1369,7 @@
         <v>58</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>185</v>
+        <v>134</v>
       </c>
       <c r="C1" s="6" t="s">
         <v>0</v>
@@ -1576,10 +1384,10 @@
         <v>57</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>186</v>
+        <v>135</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>184</v>
+        <v>133</v>
       </c>
       <c r="I1" s="6" t="s">
         <v>55</v>
@@ -1588,16 +1396,16 @@
         <v>54</v>
       </c>
       <c r="K1" s="6" t="s">
-        <v>181</v>
+        <v>130</v>
       </c>
       <c r="L1" s="6" t="s">
-        <v>183</v>
+        <v>132</v>
       </c>
       <c r="M1" s="6" t="s">
-        <v>182</v>
+        <v>131</v>
       </c>
       <c r="N1" s="6" t="s">
-        <v>187</v>
+        <v>136</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.35">
@@ -1622,10 +1430,10 @@
       <c r="G2" s="5"/>
       <c r="H2" s="5"/>
       <c r="I2" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="K2" s="4"/>
       <c r="L2" s="4"/>
@@ -1654,10 +1462,10 @@
       <c r="G3" s="5"/>
       <c r="H3" s="5"/>
       <c r="I3" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="K3" s="4"/>
       <c r="L3" s="4"/>
@@ -1686,10 +1494,10 @@
       <c r="G4" s="5"/>
       <c r="H4" s="5"/>
       <c r="I4" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="K4" s="4"/>
       <c r="L4" s="4"/>
@@ -1718,10 +1526,10 @@
       <c r="G5" s="5"/>
       <c r="H5" s="5"/>
       <c r="I5" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -1750,10 +1558,10 @@
       <c r="G6" s="5"/>
       <c r="H6" s="5"/>
       <c r="I6" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -1782,10 +1590,10 @@
       <c r="G7" s="5"/>
       <c r="H7" s="5"/>
       <c r="I7" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
@@ -1814,10 +1622,10 @@
       <c r="G8" s="5"/>
       <c r="H8" s="5"/>
       <c r="I8" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -1846,10 +1654,10 @@
       <c r="G9" s="5"/>
       <c r="H9" s="5"/>
       <c r="I9" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
@@ -1878,10 +1686,10 @@
       <c r="G10" s="5"/>
       <c r="H10" s="5"/>
       <c r="I10" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
@@ -1910,10 +1718,10 @@
       <c r="G11" s="5"/>
       <c r="H11" s="5"/>
       <c r="I11" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
@@ -1942,10 +1750,10 @@
       <c r="G12" s="5"/>
       <c r="H12" s="5"/>
       <c r="I12" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
@@ -1974,10 +1782,10 @@
       <c r="G13" s="5"/>
       <c r="H13" s="5"/>
       <c r="I13" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
@@ -2006,10 +1814,10 @@
       <c r="G14" s="5"/>
       <c r="H14" s="5"/>
       <c r="I14" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
@@ -2038,10 +1846,10 @@
       <c r="G15" s="5"/>
       <c r="H15" s="5"/>
       <c r="I15" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
@@ -2070,10 +1878,10 @@
       <c r="G16" s="5"/>
       <c r="H16" s="5"/>
       <c r="I16" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
@@ -2102,10 +1910,10 @@
       <c r="G17" s="5"/>
       <c r="H17" s="5"/>
       <c r="I17" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
@@ -2134,10 +1942,10 @@
       <c r="G18" s="5"/>
       <c r="H18" s="5"/>
       <c r="I18" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="J18" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
@@ -2166,10 +1974,10 @@
       <c r="G19" s="5"/>
       <c r="H19" s="5"/>
       <c r="I19" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
@@ -2198,10 +2006,10 @@
       <c r="G20" s="5"/>
       <c r="H20" s="5"/>
       <c r="I20" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
@@ -2230,10 +2038,10 @@
       <c r="G21" s="5"/>
       <c r="H21" s="5"/>
       <c r="I21" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
@@ -2262,10 +2070,10 @@
       <c r="G22" s="5"/>
       <c r="H22" s="5"/>
       <c r="I22" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
@@ -2294,10 +2102,10 @@
       <c r="G23" s="5"/>
       <c r="H23" s="5"/>
       <c r="I23" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
@@ -2326,10 +2134,10 @@
       <c r="G24" s="5"/>
       <c r="H24" s="5"/>
       <c r="I24" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
@@ -2358,10 +2166,10 @@
       <c r="G25" s="5"/>
       <c r="H25" s="5"/>
       <c r="I25" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
@@ -2390,10 +2198,10 @@
       <c r="G26" s="5"/>
       <c r="H26" s="5"/>
       <c r="I26" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
@@ -2425,7 +2233,7 @@
         <v>56</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
@@ -2454,10 +2262,10 @@
       <c r="G28" s="5"/>
       <c r="H28" s="5"/>
       <c r="I28" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="J28" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
@@ -2489,7 +2297,7 @@
         <v>56</v>
       </c>
       <c r="J29" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
@@ -2518,10 +2326,10 @@
       <c r="G30" s="5"/>
       <c r="H30" s="5"/>
       <c r="I30" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="J30" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
@@ -2550,10 +2358,10 @@
       <c r="G31" s="5"/>
       <c r="H31" s="5"/>
       <c r="I31" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="J31" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
@@ -2582,10 +2390,10 @@
       <c r="G32" s="5"/>
       <c r="H32" s="5"/>
       <c r="I32" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="J32" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
@@ -2617,7 +2425,7 @@
         <v>56</v>
       </c>
       <c r="J33" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
@@ -2649,7 +2457,7 @@
         <v>56</v>
       </c>
       <c r="J34" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
@@ -2681,7 +2489,7 @@
         <v>56</v>
       </c>
       <c r="J35" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
@@ -2713,7 +2521,7 @@
         <v>56</v>
       </c>
       <c r="J36" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
@@ -2742,10 +2550,10 @@
       <c r="G37" s="5"/>
       <c r="H37" s="5"/>
       <c r="I37" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="J37" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
@@ -2774,10 +2582,10 @@
       <c r="G38" s="5"/>
       <c r="H38" s="5"/>
       <c r="I38" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="J38" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
@@ -2806,10 +2614,10 @@
       <c r="G39" s="5"/>
       <c r="H39" s="5"/>
       <c r="I39" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="J39" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
@@ -2838,10 +2646,10 @@
       <c r="G40" s="5"/>
       <c r="H40" s="5"/>
       <c r="I40" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="J40" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
@@ -2870,10 +2678,10 @@
       <c r="G41" s="5"/>
       <c r="H41" s="5"/>
       <c r="I41" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="J41" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
@@ -2905,7 +2713,7 @@
         <v>56</v>
       </c>
       <c r="J42" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
@@ -2934,10 +2742,10 @@
       <c r="G43" s="5"/>
       <c r="H43" s="5"/>
       <c r="I43" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="J43" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
@@ -2966,10 +2774,10 @@
       <c r="G44" s="5"/>
       <c r="H44" s="5"/>
       <c r="I44" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="J44" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
@@ -2998,10 +2806,10 @@
       <c r="G45" s="5"/>
       <c r="H45" s="5"/>
       <c r="I45" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="J45" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
@@ -3033,7 +2841,7 @@
         <v>56</v>
       </c>
       <c r="J46" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
@@ -3126,7 +2934,7 @@
       <c r="G49" s="5"/>
       <c r="H49" s="5"/>
       <c r="I49" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="J49" s="4" t="s">
         <v>56</v>
@@ -3158,7 +2966,7 @@
       <c r="G50" s="5"/>
       <c r="H50" s="5"/>
       <c r="I50" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="J50" s="4" t="s">
         <v>56</v>
@@ -3190,7 +2998,7 @@
       <c r="G51" s="5"/>
       <c r="H51" s="5"/>
       <c r="I51" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="J51" s="4" t="s">
         <v>56</v>
@@ -3202,13 +3010,13 @@
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A52" s="21" t="s">
-        <v>116</v>
+        <v>65</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>116</v>
+        <v>65</v>
       </c>
       <c r="D52" s="15">
         <v>451560.92599999998</v>
@@ -3258,33 +3066,33 @@
   <sheetData>
     <row r="1" spans="1:8" ht="39" x14ac:dyDescent="0.35">
       <c r="A1" s="38" t="s">
-        <v>118</v>
+        <v>67</v>
       </c>
       <c r="B1" s="38" t="s">
-        <v>192</v>
+        <v>141</v>
       </c>
       <c r="C1" s="38" t="s">
-        <v>185</v>
+        <v>134</v>
       </c>
       <c r="D1" s="38" t="s">
-        <v>119</v>
+        <v>68</v>
       </c>
       <c r="E1" s="38" t="s">
-        <v>120</v>
+        <v>69</v>
       </c>
       <c r="F1" s="38" t="s">
-        <v>114</v>
+        <v>63</v>
       </c>
       <c r="G1" s="38" t="s">
-        <v>115</v>
+        <v>64</v>
       </c>
       <c r="H1" s="38" t="s">
-        <v>191</v>
+        <v>140</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="32" t="s">
-        <v>121</v>
+        <v>70</v>
       </c>
       <c r="B2" s="32" t="str">
         <f>F2&amp;"-"&amp;G2</f>
@@ -3294,13 +3102,13 @@
         <v>56</v>
       </c>
       <c r="D2" s="32" t="s">
-        <v>122</v>
+        <v>71</v>
       </c>
       <c r="E2" s="33" t="s">
-        <v>123</v>
+        <v>72</v>
       </c>
       <c r="F2" s="13" t="s">
-        <v>116</v>
+        <v>65</v>
       </c>
       <c r="G2" s="19" t="s">
         <v>51</v>
@@ -3311,7 +3119,7 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="28" t="s">
-        <v>124</v>
+        <v>73</v>
       </c>
       <c r="B3" s="28" t="str">
         <f t="shared" ref="B3:B56" si="0">F3&amp;"-"&amp;G3</f>
@@ -3321,10 +3129,10 @@
         <v>56</v>
       </c>
       <c r="D3" s="28" t="s">
-        <v>122</v>
+        <v>71</v>
       </c>
       <c r="E3" s="29" t="s">
-        <v>123</v>
+        <v>72</v>
       </c>
       <c r="F3" s="11" t="s">
         <v>51</v>
@@ -3333,12 +3141,12 @@
         <v>49</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="28" t="s">
-        <v>125</v>
+        <v>74</v>
       </c>
       <c r="B4" s="28" t="str">
         <f t="shared" si="0"/>
@@ -3348,10 +3156,10 @@
         <v>56</v>
       </c>
       <c r="D4" s="28" t="s">
-        <v>122</v>
+        <v>71</v>
       </c>
       <c r="E4" s="29" t="s">
-        <v>123</v>
+        <v>72</v>
       </c>
       <c r="F4" s="11" t="s">
         <v>49</v>
@@ -3360,12 +3168,12 @@
         <v>48</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="28" t="s">
-        <v>126</v>
+        <v>75</v>
       </c>
       <c r="B5" s="28" t="str">
         <f t="shared" si="0"/>
@@ -3375,10 +3183,10 @@
         <v>56</v>
       </c>
       <c r="D5" s="28" t="s">
-        <v>122</v>
+        <v>71</v>
       </c>
       <c r="E5" s="29" t="s">
-        <v>123</v>
+        <v>72</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>48</v>
@@ -3387,12 +3195,12 @@
         <v>47</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="28" t="s">
-        <v>127</v>
+        <v>76</v>
       </c>
       <c r="B6" s="28" t="str">
         <f t="shared" si="0"/>
@@ -3402,10 +3210,10 @@
         <v>56</v>
       </c>
       <c r="D6" s="28" t="s">
-        <v>122</v>
+        <v>71</v>
       </c>
       <c r="E6" s="29" t="s">
-        <v>123</v>
+        <v>72</v>
       </c>
       <c r="F6" s="11" t="s">
         <v>47</v>
@@ -3414,12 +3222,12 @@
         <v>46</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="28" t="s">
-        <v>128</v>
+        <v>77</v>
       </c>
       <c r="B7" s="28" t="str">
         <f t="shared" si="0"/>
@@ -3430,7 +3238,7 @@
       </c>
       <c r="D7" s="28"/>
       <c r="E7" s="29" t="s">
-        <v>123</v>
+        <v>72</v>
       </c>
       <c r="F7" s="11" t="s">
         <v>46</v>
@@ -3439,12 +3247,12 @@
         <v>40</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="28" t="s">
-        <v>129</v>
+        <v>78</v>
       </c>
       <c r="B8" s="28" t="str">
         <f t="shared" si="0"/>
@@ -3454,10 +3262,10 @@
         <v>56</v>
       </c>
       <c r="D8" s="28" t="s">
-        <v>130</v>
+        <v>79</v>
       </c>
       <c r="E8" s="29" t="s">
-        <v>123</v>
+        <v>72</v>
       </c>
       <c r="F8" s="11" t="s">
         <v>40</v>
@@ -3466,12 +3274,12 @@
         <v>44</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="28" t="s">
-        <v>131</v>
+        <v>80</v>
       </c>
       <c r="B9" s="28" t="str">
         <f t="shared" si="0"/>
@@ -3481,10 +3289,10 @@
         <v>56</v>
       </c>
       <c r="D9" s="28" t="s">
-        <v>130</v>
+        <v>79</v>
       </c>
       <c r="E9" s="29" t="s">
-        <v>123</v>
+        <v>72</v>
       </c>
       <c r="F9" s="11" t="s">
         <v>44</v>
@@ -3493,12 +3301,12 @@
         <v>30</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="28" t="s">
-        <v>132</v>
+        <v>81</v>
       </c>
       <c r="B10" s="28" t="str">
         <f t="shared" si="0"/>
@@ -3508,10 +3316,10 @@
         <v>56</v>
       </c>
       <c r="D10" s="28" t="s">
-        <v>130</v>
+        <v>79</v>
       </c>
       <c r="E10" s="29" t="s">
-        <v>123</v>
+        <v>72</v>
       </c>
       <c r="F10" s="11" t="s">
         <v>30</v>
@@ -3520,12 +3328,12 @@
         <v>43</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" s="28" t="s">
-        <v>133</v>
+        <v>82</v>
       </c>
       <c r="B11" s="28" t="str">
         <f t="shared" si="0"/>
@@ -3535,10 +3343,10 @@
         <v>56</v>
       </c>
       <c r="D11" s="28" t="s">
-        <v>130</v>
+        <v>79</v>
       </c>
       <c r="E11" s="29" t="s">
-        <v>123</v>
+        <v>72</v>
       </c>
       <c r="F11" s="11" t="s">
         <v>43</v>
@@ -3547,12 +3355,12 @@
         <v>50</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A12" s="30" t="s">
-        <v>134</v>
+        <v>83</v>
       </c>
       <c r="B12" s="30" t="str">
         <f t="shared" si="0"/>
@@ -3562,16 +3370,16 @@
         <v>56</v>
       </c>
       <c r="D12" s="30" t="s">
-        <v>130</v>
+        <v>79</v>
       </c>
       <c r="E12" s="31" t="s">
-        <v>123</v>
+        <v>72</v>
       </c>
       <c r="F12" s="12" t="s">
         <v>50</v>
       </c>
       <c r="G12" s="18" t="s">
-        <v>116</v>
+        <v>65</v>
       </c>
       <c r="H12" s="4" t="s">
         <v>56</v>
@@ -3579,7 +3387,7 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" s="32" t="s">
-        <v>135</v>
+        <v>84</v>
       </c>
       <c r="B13" s="32" t="str">
         <f t="shared" si="0"/>
@@ -3589,13 +3397,13 @@
         <v>56</v>
       </c>
       <c r="D13" s="32" t="s">
-        <v>136</v>
+        <v>85</v>
       </c>
       <c r="E13" s="33" t="s">
-        <v>137</v>
+        <v>86</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>116</v>
+        <v>65</v>
       </c>
       <c r="G13" s="19" t="s">
         <v>45</v>
@@ -3606,7 +3414,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="28" t="s">
-        <v>138</v>
+        <v>87</v>
       </c>
       <c r="B14" s="28" t="str">
         <f t="shared" si="0"/>
@@ -3616,10 +3424,10 @@
         <v>56</v>
       </c>
       <c r="D14" s="28" t="s">
-        <v>136</v>
+        <v>85</v>
       </c>
       <c r="E14" s="29" t="s">
-        <v>137</v>
+        <v>86</v>
       </c>
       <c r="F14" s="11" t="s">
         <v>45</v>
@@ -3628,12 +3436,12 @@
         <v>36</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" s="28" t="s">
-        <v>139</v>
+        <v>88</v>
       </c>
       <c r="B15" s="28" t="str">
         <f t="shared" si="0"/>
@@ -3643,10 +3451,10 @@
         <v>56</v>
       </c>
       <c r="D15" s="28" t="s">
-        <v>136</v>
+        <v>85</v>
       </c>
       <c r="E15" s="29" t="s">
-        <v>137</v>
+        <v>86</v>
       </c>
       <c r="F15" s="11" t="s">
         <v>36</v>
@@ -3655,12 +3463,12 @@
         <v>37</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" s="28" t="s">
-        <v>140</v>
+        <v>89</v>
       </c>
       <c r="B16" s="28" t="str">
         <f t="shared" si="0"/>
@@ -3670,10 +3478,10 @@
         <v>56</v>
       </c>
       <c r="D16" s="28" t="s">
-        <v>136</v>
+        <v>85</v>
       </c>
       <c r="E16" s="29" t="s">
-        <v>137</v>
+        <v>86</v>
       </c>
       <c r="F16" s="11" t="s">
         <v>37</v>
@@ -3682,12 +3490,12 @@
         <v>6</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" s="28" t="s">
-        <v>141</v>
+        <v>90</v>
       </c>
       <c r="B17" s="28" t="str">
         <f t="shared" si="0"/>
@@ -3697,10 +3505,10 @@
         <v>56</v>
       </c>
       <c r="D17" s="28" t="s">
-        <v>136</v>
+        <v>85</v>
       </c>
       <c r="E17" s="29" t="s">
-        <v>137</v>
+        <v>86</v>
       </c>
       <c r="F17" s="11" t="s">
         <v>6</v>
@@ -3709,12 +3517,12 @@
         <v>38</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" s="28" t="s">
-        <v>142</v>
+        <v>91</v>
       </c>
       <c r="B18" s="28" t="str">
         <f t="shared" si="0"/>
@@ -3725,7 +3533,7 @@
       </c>
       <c r="D18" s="28"/>
       <c r="E18" s="29" t="s">
-        <v>137</v>
+        <v>86</v>
       </c>
       <c r="F18" s="11" t="s">
         <v>38</v>
@@ -3734,12 +3542,12 @@
         <v>22</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" s="28" t="s">
-        <v>143</v>
+        <v>92</v>
       </c>
       <c r="B19" s="28" t="str">
         <f t="shared" si="0"/>
@@ -3749,10 +3557,10 @@
         <v>56</v>
       </c>
       <c r="D19" s="28" t="s">
-        <v>144</v>
+        <v>93</v>
       </c>
       <c r="E19" s="29" t="s">
-        <v>137</v>
+        <v>86</v>
       </c>
       <c r="F19" s="11" t="s">
         <v>22</v>
@@ -3761,12 +3569,12 @@
         <v>18</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" s="28" t="s">
-        <v>145</v>
+        <v>94</v>
       </c>
       <c r="B20" s="28" t="str">
         <f t="shared" si="0"/>
@@ -3776,10 +3584,10 @@
         <v>56</v>
       </c>
       <c r="D20" s="28" t="s">
-        <v>144</v>
+        <v>93</v>
       </c>
       <c r="E20" s="29" t="s">
-        <v>137</v>
+        <v>86</v>
       </c>
       <c r="F20" s="11" t="s">
         <v>18</v>
@@ -3788,12 +3596,12 @@
         <v>27</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" s="28" t="s">
-        <v>146</v>
+        <v>95</v>
       </c>
       <c r="B21" s="28" t="str">
         <f t="shared" si="0"/>
@@ -3803,10 +3611,10 @@
         <v>56</v>
       </c>
       <c r="D21" s="28" t="s">
-        <v>144</v>
+        <v>93</v>
       </c>
       <c r="E21" s="29" t="s">
-        <v>137</v>
+        <v>86</v>
       </c>
       <c r="F21" s="11" t="s">
         <v>27</v>
@@ -3815,12 +3623,12 @@
         <v>31</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" s="28" t="s">
-        <v>147</v>
+        <v>96</v>
       </c>
       <c r="B22" s="28" t="str">
         <f t="shared" si="0"/>
@@ -3830,10 +3638,10 @@
         <v>56</v>
       </c>
       <c r="D22" s="28" t="s">
-        <v>144</v>
+        <v>93</v>
       </c>
       <c r="E22" s="29" t="s">
-        <v>137</v>
+        <v>86</v>
       </c>
       <c r="F22" s="11" t="s">
         <v>31</v>
@@ -3842,12 +3650,12 @@
         <v>39</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A23" s="34" t="s">
-        <v>148</v>
+        <v>97</v>
       </c>
       <c r="B23" s="34" t="str">
         <f t="shared" si="0"/>
@@ -3857,319 +3665,319 @@
         <v>56</v>
       </c>
       <c r="D23" s="34" t="s">
-        <v>144</v>
+        <v>93</v>
       </c>
       <c r="E23" s="35" t="s">
-        <v>137</v>
+        <v>86</v>
       </c>
       <c r="F23" s="14" t="s">
         <v>39</v>
       </c>
       <c r="G23" s="20" t="s">
-        <v>116</v>
+        <v>65</v>
       </c>
       <c r="H23" s="4" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A24" s="40" t="s">
-        <v>193</v>
-      </c>
-      <c r="B24" s="40" t="str">
+      <c r="A24" s="26" t="s">
+        <v>142</v>
+      </c>
+      <c r="B24" s="26" t="str">
         <f t="shared" si="0"/>
         <v>OSS-D05</v>
       </c>
-      <c r="C24" s="40" t="s">
-        <v>56</v>
-      </c>
-      <c r="D24" s="40" t="s">
+      <c r="C24" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="D24" s="26" t="s">
+        <v>98</v>
+      </c>
+      <c r="E24" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="F24" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="G24" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A25" s="28" t="s">
+        <v>143</v>
+      </c>
+      <c r="B25" s="28" t="str">
+        <f t="shared" si="0"/>
+        <v>D05-C04</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D25" s="28" t="s">
+        <v>98</v>
+      </c>
+      <c r="E25" s="29" t="s">
+        <v>99</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G25" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A26" s="28" t="s">
+        <v>144</v>
+      </c>
+      <c r="B26" s="28" t="str">
+        <f t="shared" si="0"/>
+        <v>C04-C03</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D26" s="28" t="s">
+        <v>98</v>
+      </c>
+      <c r="E26" s="29" t="s">
+        <v>99</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G26" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A27" s="28" t="s">
+        <v>145</v>
+      </c>
+      <c r="B27" s="28" t="str">
+        <f t="shared" si="0"/>
+        <v>C03-B02</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D27" s="28" t="s">
+        <v>98</v>
+      </c>
+      <c r="E27" s="29" t="s">
+        <v>99</v>
+      </c>
+      <c r="F27" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="G27" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A28" s="28" t="s">
+        <v>146</v>
+      </c>
+      <c r="B28" s="28" t="str">
+        <f t="shared" si="0"/>
+        <v>B02-A01</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D28" s="28" t="s">
+        <v>98</v>
+      </c>
+      <c r="E28" s="29" t="s">
+        <v>99</v>
+      </c>
+      <c r="F28" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="G28" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A29" s="28" t="s">
+        <v>147</v>
+      </c>
+      <c r="B29" s="28" t="str">
+        <f t="shared" si="0"/>
+        <v>A01-A02</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D29" s="28"/>
+      <c r="E29" s="29" t="s">
+        <v>99</v>
+      </c>
+      <c r="F29" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G29" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A30" s="28" t="s">
+        <v>148</v>
+      </c>
+      <c r="B30" s="28" t="str">
+        <f t="shared" si="0"/>
+        <v>A02-A03</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D30" s="28" t="s">
+        <v>100</v>
+      </c>
+      <c r="E30" s="29" t="s">
+        <v>99</v>
+      </c>
+      <c r="F30" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="G30" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A31" s="28" t="s">
         <v>149</v>
       </c>
-      <c r="E24" s="41" t="s">
+      <c r="B31" s="28" t="str">
+        <f t="shared" si="0"/>
+        <v>A03-B03</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D31" s="28" t="s">
+        <v>100</v>
+      </c>
+      <c r="E31" s="29" t="s">
+        <v>99</v>
+      </c>
+      <c r="F31" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="G31" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A32" s="28" t="s">
         <v>150</v>
       </c>
-      <c r="F24" s="40" t="s">
-        <v>116</v>
-      </c>
-      <c r="G24" s="40" t="s">
-        <v>53</v>
-      </c>
-      <c r="H24" s="42" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A25" s="43" t="s">
-        <v>194</v>
-      </c>
-      <c r="B25" s="43" t="str">
-        <f t="shared" si="0"/>
-        <v>D05-C04</v>
-      </c>
-      <c r="C25" s="44" t="s">
-        <v>56</v>
-      </c>
-      <c r="D25" s="43" t="s">
-        <v>149</v>
-      </c>
-      <c r="E25" s="45" t="s">
-        <v>150</v>
-      </c>
-      <c r="F25" s="44" t="s">
-        <v>53</v>
-      </c>
-      <c r="G25" s="43" t="s">
-        <v>26</v>
-      </c>
-      <c r="H25" s="42" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A26" s="43" t="s">
-        <v>195</v>
-      </c>
-      <c r="B26" s="43" t="str">
-        <f t="shared" si="0"/>
-        <v>C04-C03</v>
-      </c>
-      <c r="C26" s="44" t="s">
-        <v>56</v>
-      </c>
-      <c r="D26" s="43" t="s">
-        <v>149</v>
-      </c>
-      <c r="E26" s="45" t="s">
-        <v>150</v>
-      </c>
-      <c r="F26" s="44" t="s">
-        <v>26</v>
-      </c>
-      <c r="G26" s="43" t="s">
-        <v>34</v>
-      </c>
-      <c r="H26" s="42" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A27" s="43" t="s">
-        <v>196</v>
-      </c>
-      <c r="B27" s="43" t="str">
-        <f t="shared" si="0"/>
-        <v>C03-B02</v>
-      </c>
-      <c r="C27" s="44" t="s">
-        <v>56</v>
-      </c>
-      <c r="D27" s="43" t="s">
-        <v>149</v>
-      </c>
-      <c r="E27" s="45" t="s">
-        <v>150</v>
-      </c>
-      <c r="F27" s="46" t="s">
-        <v>34</v>
-      </c>
-      <c r="G27" s="47" t="s">
-        <v>11</v>
-      </c>
-      <c r="H27" s="42" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A28" s="43" t="s">
-        <v>197</v>
-      </c>
-      <c r="B28" s="43" t="str">
-        <f t="shared" si="0"/>
-        <v>B02-A01</v>
-      </c>
-      <c r="C28" s="44" t="s">
-        <v>56</v>
-      </c>
-      <c r="D28" s="43" t="s">
-        <v>149</v>
-      </c>
-      <c r="E28" s="45" t="s">
-        <v>150</v>
-      </c>
-      <c r="F28" s="46" t="s">
-        <v>11</v>
-      </c>
-      <c r="G28" s="47" t="s">
-        <v>14</v>
-      </c>
-      <c r="H28" s="42" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A29" s="43" t="s">
-        <v>198</v>
-      </c>
-      <c r="B29" s="43" t="str">
-        <f t="shared" si="0"/>
-        <v>A01-A02</v>
-      </c>
-      <c r="C29" s="44" t="s">
-        <v>56</v>
-      </c>
-      <c r="D29" s="43"/>
-      <c r="E29" s="45" t="s">
-        <v>150</v>
-      </c>
-      <c r="F29" s="46" t="s">
-        <v>14</v>
-      </c>
-      <c r="G29" s="47" t="s">
-        <v>8</v>
-      </c>
-      <c r="H29" s="42" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A30" s="43" t="s">
-        <v>199</v>
-      </c>
-      <c r="B30" s="43" t="str">
-        <f t="shared" si="0"/>
-        <v>A02-A03</v>
-      </c>
-      <c r="C30" s="44" t="s">
-        <v>56</v>
-      </c>
-      <c r="D30" s="43" t="s">
+      <c r="B32" s="28" t="str">
+        <f t="shared" si="0"/>
+        <v>B03-B04</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D32" s="28" t="s">
+        <v>100</v>
+      </c>
+      <c r="E32" s="29" t="s">
+        <v>99</v>
+      </c>
+      <c r="F32" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="G32" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A33" s="28" t="s">
         <v>151</v>
       </c>
-      <c r="E30" s="45" t="s">
-        <v>150</v>
-      </c>
-      <c r="F30" s="46" t="s">
-        <v>8</v>
-      </c>
-      <c r="G30" s="47" t="s">
-        <v>5</v>
-      </c>
-      <c r="H30" s="42" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A31" s="43" t="s">
-        <v>200</v>
-      </c>
-      <c r="B31" s="43" t="str">
-        <f t="shared" si="0"/>
-        <v>A03-B03</v>
-      </c>
-      <c r="C31" s="44" t="s">
-        <v>56</v>
-      </c>
-      <c r="D31" s="43" t="s">
-        <v>151</v>
-      </c>
-      <c r="E31" s="45" t="s">
-        <v>150</v>
-      </c>
-      <c r="F31" s="46" t="s">
-        <v>5</v>
-      </c>
-      <c r="G31" s="47" t="s">
-        <v>12</v>
-      </c>
-      <c r="H31" s="42" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A32" s="43" t="s">
-        <v>201</v>
-      </c>
-      <c r="B32" s="43" t="str">
-        <f t="shared" si="0"/>
-        <v>B03-B04</v>
-      </c>
-      <c r="C32" s="44" t="s">
-        <v>56</v>
-      </c>
-      <c r="D32" s="43" t="s">
-        <v>151</v>
-      </c>
-      <c r="E32" s="45" t="s">
-        <v>150</v>
-      </c>
-      <c r="F32" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="G32" s="47" t="s">
+      <c r="B33" s="28" t="str">
+        <f t="shared" si="0"/>
+        <v>B04-D06</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D33" s="28" t="s">
+        <v>100</v>
+      </c>
+      <c r="E33" s="29" t="s">
+        <v>99</v>
+      </c>
+      <c r="F33" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="H32" s="42" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A33" s="43" t="s">
-        <v>202</v>
-      </c>
-      <c r="B33" s="43" t="str">
-        <f t="shared" si="0"/>
-        <v>B04-D06</v>
-      </c>
-      <c r="C33" s="44" t="s">
-        <v>56</v>
-      </c>
-      <c r="D33" s="43" t="s">
-        <v>151</v>
-      </c>
-      <c r="E33" s="45" t="s">
-        <v>150</v>
-      </c>
-      <c r="F33" s="46" t="s">
-        <v>15</v>
-      </c>
-      <c r="G33" s="47" t="s">
+      <c r="G33" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="H33" s="42" t="s">
-        <v>113</v>
+      <c r="H33" s="4" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="48" t="s">
-        <v>152</v>
-      </c>
-      <c r="B34" s="48" t="str">
+      <c r="A34" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="B34" s="30" t="str">
         <f t="shared" si="0"/>
         <v>D06-OSS</v>
       </c>
-      <c r="C34" s="49" t="s">
-        <v>56</v>
-      </c>
-      <c r="D34" s="48" t="s">
-        <v>151</v>
-      </c>
-      <c r="E34" s="50" t="s">
-        <v>150</v>
-      </c>
-      <c r="F34" s="51" t="s">
+      <c r="C34" s="34" t="s">
+        <v>56</v>
+      </c>
+      <c r="D34" s="30" t="s">
+        <v>100</v>
+      </c>
+      <c r="E34" s="31" t="s">
+        <v>99</v>
+      </c>
+      <c r="F34" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="G34" s="52" t="s">
-        <v>116</v>
-      </c>
-      <c r="H34" s="42" t="s">
+      <c r="G34" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="H34" s="4" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A35" s="32" t="s">
-        <v>153</v>
+        <v>102</v>
       </c>
       <c r="B35" s="32" t="str">
         <f t="shared" si="0"/>
@@ -4179,13 +3987,13 @@
         <v>56</v>
       </c>
       <c r="D35" s="32" t="s">
-        <v>154</v>
+        <v>103</v>
       </c>
       <c r="E35" s="33" t="s">
-        <v>155</v>
+        <v>104</v>
       </c>
       <c r="F35" s="13" t="s">
-        <v>116</v>
+        <v>65</v>
       </c>
       <c r="G35" s="19" t="s">
         <v>7</v>
@@ -4196,7 +4004,7 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A36" s="28" t="s">
-        <v>156</v>
+        <v>105</v>
       </c>
       <c r="B36" s="28" t="str">
         <f t="shared" si="0"/>
@@ -4206,10 +4014,10 @@
         <v>56</v>
       </c>
       <c r="D36" s="28" t="s">
-        <v>154</v>
+        <v>103</v>
       </c>
       <c r="E36" s="29" t="s">
-        <v>155</v>
+        <v>104</v>
       </c>
       <c r="F36" s="11" t="s">
         <v>7</v>
@@ -4218,12 +4026,12 @@
         <v>21</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A37" s="28" t="s">
-        <v>157</v>
+        <v>106</v>
       </c>
       <c r="B37" s="28" t="str">
         <f t="shared" si="0"/>
@@ -4233,10 +4041,10 @@
         <v>56</v>
       </c>
       <c r="D37" s="28" t="s">
-        <v>154</v>
+        <v>103</v>
       </c>
       <c r="E37" s="29" t="s">
-        <v>155</v>
+        <v>104</v>
       </c>
       <c r="F37" s="11" t="s">
         <v>21</v>
@@ -4245,12 +4053,12 @@
         <v>16</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A38" s="28" t="s">
-        <v>158</v>
+        <v>107</v>
       </c>
       <c r="B38" s="28" t="str">
         <f t="shared" si="0"/>
@@ -4260,10 +4068,10 @@
         <v>56</v>
       </c>
       <c r="D38" s="28" t="s">
-        <v>154</v>
+        <v>103</v>
       </c>
       <c r="E38" s="29" t="s">
-        <v>155</v>
+        <v>104</v>
       </c>
       <c r="F38" s="11" t="s">
         <v>16</v>
@@ -4272,12 +4080,12 @@
         <v>4</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A39" s="28" t="s">
-        <v>159</v>
+        <v>108</v>
       </c>
       <c r="B39" s="28" t="str">
         <f t="shared" si="0"/>
@@ -4287,10 +4095,10 @@
         <v>56</v>
       </c>
       <c r="D39" s="28" t="s">
-        <v>154</v>
+        <v>103</v>
       </c>
       <c r="E39" s="29" t="s">
-        <v>155</v>
+        <v>104</v>
       </c>
       <c r="F39" s="11" t="s">
         <v>4</v>
@@ -4299,12 +4107,12 @@
         <v>10</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A40" s="28" t="s">
-        <v>160</v>
+        <v>109</v>
       </c>
       <c r="B40" s="28" t="str">
         <f t="shared" si="0"/>
@@ -4315,7 +4123,7 @@
       </c>
       <c r="D40" s="28"/>
       <c r="E40" s="29" t="s">
-        <v>155</v>
+        <v>104</v>
       </c>
       <c r="F40" s="11" t="s">
         <v>10</v>
@@ -4324,12 +4132,12 @@
         <v>17</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A41" s="28" t="s">
-        <v>161</v>
+        <v>110</v>
       </c>
       <c r="B41" s="28" t="str">
         <f t="shared" si="0"/>
@@ -4339,10 +4147,10 @@
         <v>56</v>
       </c>
       <c r="D41" s="28" t="s">
-        <v>162</v>
+        <v>111</v>
       </c>
       <c r="E41" s="29" t="s">
-        <v>155</v>
+        <v>104</v>
       </c>
       <c r="F41" s="11" t="s">
         <v>17</v>
@@ -4351,12 +4159,12 @@
         <v>20</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A42" s="28" t="s">
-        <v>163</v>
+        <v>112</v>
       </c>
       <c r="B42" s="28" t="str">
         <f t="shared" si="0"/>
@@ -4366,10 +4174,10 @@
         <v>56</v>
       </c>
       <c r="D42" s="28" t="s">
-        <v>162</v>
+        <v>111</v>
       </c>
       <c r="E42" s="29" t="s">
-        <v>155</v>
+        <v>104</v>
       </c>
       <c r="F42" s="11" t="s">
         <v>20</v>
@@ -4378,12 +4186,12 @@
         <v>9</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A43" s="28" t="s">
-        <v>164</v>
+        <v>113</v>
       </c>
       <c r="B43" s="28" t="str">
         <f t="shared" si="0"/>
@@ -4393,10 +4201,10 @@
         <v>56</v>
       </c>
       <c r="D43" s="28" t="s">
-        <v>162</v>
+        <v>111</v>
       </c>
       <c r="E43" s="29" t="s">
-        <v>155</v>
+        <v>104</v>
       </c>
       <c r="F43" s="11" t="s">
         <v>9</v>
@@ -4405,12 +4213,12 @@
         <v>13</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A44" s="28" t="s">
-        <v>165</v>
+        <v>114</v>
       </c>
       <c r="B44" s="28" t="str">
         <f t="shared" si="0"/>
@@ -4420,10 +4228,10 @@
         <v>56</v>
       </c>
       <c r="D44" s="28" t="s">
-        <v>162</v>
+        <v>111</v>
       </c>
       <c r="E44" s="29" t="s">
-        <v>155</v>
+        <v>104</v>
       </c>
       <c r="F44" s="11" t="s">
         <v>13</v>
@@ -4432,12 +4240,12 @@
         <v>41</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A45" s="34" t="s">
-        <v>166</v>
+        <v>115</v>
       </c>
       <c r="B45" s="34" t="str">
         <f t="shared" si="0"/>
@@ -4447,16 +4255,16 @@
         <v>56</v>
       </c>
       <c r="D45" s="34" t="s">
-        <v>162</v>
+        <v>111</v>
       </c>
       <c r="E45" s="35" t="s">
-        <v>155</v>
+        <v>104</v>
       </c>
       <c r="F45" s="14" t="s">
         <v>41</v>
       </c>
       <c r="G45" s="20" t="s">
-        <v>116</v>
+        <v>65</v>
       </c>
       <c r="H45" s="4" t="s">
         <v>56</v>
@@ -4464,7 +4272,7 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A46" s="26" t="s">
-        <v>167</v>
+        <v>116</v>
       </c>
       <c r="B46" s="26" t="str">
         <f t="shared" si="0"/>
@@ -4474,13 +4282,13 @@
         <v>56</v>
       </c>
       <c r="D46" s="26" t="s">
-        <v>168</v>
+        <v>117</v>
       </c>
       <c r="E46" s="27" t="s">
-        <v>169</v>
+        <v>118</v>
       </c>
       <c r="F46" s="10" t="s">
-        <v>116</v>
+        <v>65</v>
       </c>
       <c r="G46" s="16" t="s">
         <v>23</v>
@@ -4491,7 +4299,7 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A47" s="28" t="s">
-        <v>170</v>
+        <v>119</v>
       </c>
       <c r="B47" s="28" t="str">
         <f t="shared" si="0"/>
@@ -4501,10 +4309,10 @@
         <v>56</v>
       </c>
       <c r="D47" s="28" t="s">
-        <v>168</v>
+        <v>117</v>
       </c>
       <c r="E47" s="29" t="s">
-        <v>169</v>
+        <v>118</v>
       </c>
       <c r="F47" s="11" t="s">
         <v>23</v>
@@ -4513,12 +4321,12 @@
         <v>19</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A48" s="28" t="s">
-        <v>171</v>
+        <v>120</v>
       </c>
       <c r="B48" s="28" t="str">
         <f t="shared" si="0"/>
@@ -4528,10 +4336,10 @@
         <v>56</v>
       </c>
       <c r="D48" s="28" t="s">
-        <v>168</v>
+        <v>117</v>
       </c>
       <c r="E48" s="29" t="s">
-        <v>169</v>
+        <v>118</v>
       </c>
       <c r="F48" s="11" t="s">
         <v>19</v>
@@ -4540,12 +4348,12 @@
         <v>35</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A49" s="28" t="s">
-        <v>172</v>
+        <v>121</v>
       </c>
       <c r="B49" s="28" t="str">
         <f t="shared" si="0"/>
@@ -4555,10 +4363,10 @@
         <v>56</v>
       </c>
       <c r="D49" s="28" t="s">
-        <v>168</v>
+        <v>117</v>
       </c>
       <c r="E49" s="29" t="s">
-        <v>169</v>
+        <v>118</v>
       </c>
       <c r="F49" s="11" t="s">
         <v>35</v>
@@ -4567,12 +4375,12 @@
         <v>29</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A50" s="28" t="s">
-        <v>173</v>
+        <v>122</v>
       </c>
       <c r="B50" s="28" t="str">
         <f t="shared" si="0"/>
@@ -4582,10 +4390,10 @@
         <v>56</v>
       </c>
       <c r="D50" s="28" t="s">
-        <v>168</v>
+        <v>117</v>
       </c>
       <c r="E50" s="29" t="s">
-        <v>169</v>
+        <v>118</v>
       </c>
       <c r="F50" s="11" t="s">
         <v>29</v>
@@ -4594,12 +4402,12 @@
         <v>24</v>
       </c>
       <c r="H50" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A51" s="28" t="s">
-        <v>174</v>
+        <v>123</v>
       </c>
       <c r="B51" s="28" t="str">
         <f t="shared" si="0"/>
@@ -4610,7 +4418,7 @@
       </c>
       <c r="D51" s="28"/>
       <c r="E51" s="29" t="s">
-        <v>169</v>
+        <v>118</v>
       </c>
       <c r="F51" s="11" t="s">
         <v>24</v>
@@ -4619,12 +4427,12 @@
         <v>28</v>
       </c>
       <c r="H51" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A52" s="28" t="s">
-        <v>175</v>
+        <v>124</v>
       </c>
       <c r="B52" s="28" t="str">
         <f t="shared" si="0"/>
@@ -4634,10 +4442,10 @@
         <v>56</v>
       </c>
       <c r="D52" s="28" t="s">
-        <v>176</v>
+        <v>125</v>
       </c>
       <c r="E52" s="29" t="s">
-        <v>169</v>
+        <v>118</v>
       </c>
       <c r="F52" s="11" t="s">
         <v>28</v>
@@ -4646,12 +4454,12 @@
         <v>32</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A53" s="28" t="s">
-        <v>177</v>
+        <v>126</v>
       </c>
       <c r="B53" s="28" t="str">
         <f t="shared" si="0"/>
@@ -4661,10 +4469,10 @@
         <v>56</v>
       </c>
       <c r="D53" s="28" t="s">
-        <v>176</v>
+        <v>125</v>
       </c>
       <c r="E53" s="29" t="s">
-        <v>169</v>
+        <v>118</v>
       </c>
       <c r="F53" s="11" t="s">
         <v>32</v>
@@ -4673,12 +4481,12 @@
         <v>25</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A54" s="28" t="s">
-        <v>178</v>
+        <v>127</v>
       </c>
       <c r="B54" s="28" t="str">
         <f t="shared" si="0"/>
@@ -4688,10 +4496,10 @@
         <v>56</v>
       </c>
       <c r="D54" s="28" t="s">
-        <v>176</v>
+        <v>125</v>
       </c>
       <c r="E54" s="29" t="s">
-        <v>169</v>
+        <v>118</v>
       </c>
       <c r="F54" s="11" t="s">
         <v>25</v>
@@ -4700,12 +4508,12 @@
         <v>33</v>
       </c>
       <c r="H54" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A55" s="28" t="s">
-        <v>179</v>
+        <v>128</v>
       </c>
       <c r="B55" s="28" t="str">
         <f t="shared" si="0"/>
@@ -4715,10 +4523,10 @@
         <v>56</v>
       </c>
       <c r="D55" s="28" t="s">
-        <v>176</v>
+        <v>125</v>
       </c>
       <c r="E55" s="29" t="s">
-        <v>169</v>
+        <v>118</v>
       </c>
       <c r="F55" s="11" t="s">
         <v>33</v>
@@ -4727,12 +4535,12 @@
         <v>52</v>
       </c>
       <c r="H55" s="4" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A56" s="30" t="s">
-        <v>180</v>
+        <v>129</v>
       </c>
       <c r="B56" s="30" t="str">
         <f t="shared" si="0"/>
@@ -4742,16 +4550,16 @@
         <v>56</v>
       </c>
       <c r="D56" s="30" t="s">
-        <v>176</v>
+        <v>125</v>
       </c>
       <c r="E56" s="31" t="s">
-        <v>169</v>
+        <v>118</v>
       </c>
       <c r="F56" s="12" t="s">
         <v>52</v>
       </c>
       <c r="G56" s="18" t="s">
-        <v>116</v>
+        <v>65</v>
       </c>
       <c r="H56" s="4" t="s">
         <v>56</v>
@@ -4768,24 +4576,22 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{253CB1B5-BB14-4D72-BAB0-6BB79BEC2624}">
-  <dimension ref="A1:H57"/>
+  <dimension ref="A1:F57"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.26953125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8.90625" customWidth="1"/>
     <col min="4" max="4" width="9.36328125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.36328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.453125" customWidth="1"/>
-    <col min="7" max="7" width="10.6328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.6328125" customWidth="1"/>
+    <col min="6" max="6" width="10.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
         <v>58</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>185</v>
+        <v>134</v>
       </c>
       <c r="C1" s="6" t="s">
         <v>0</v>
@@ -4796,17 +4602,11 @@
       <c r="E1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F1" s="7" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
@@ -4822,17 +4622,11 @@
       <c r="E2" s="15">
         <v>5926740.4285000004</v>
       </c>
-      <c r="F2" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F2" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
@@ -4848,17 +4642,11 @@
       <c r="E3" s="15">
         <v>5926754.4106999999</v>
       </c>
-      <c r="F3" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F3" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
@@ -4874,17 +4662,11 @@
       <c r="E4" s="15">
         <v>5926765.4616999999</v>
       </c>
-      <c r="F4" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F4" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -4900,17 +4682,11 @@
       <c r="E5" s="15">
         <v>5926776.5153000001</v>
       </c>
-      <c r="F5" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F5" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
@@ -4926,17 +4702,11 @@
       <c r="E6" s="15">
         <v>5926787.9123999998</v>
       </c>
-      <c r="F6" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F6" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>17</v>
       </c>
@@ -4952,17 +4722,11 @@
       <c r="E7" s="15">
         <v>5926798.8937999997</v>
       </c>
-      <c r="F7" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F7" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>20</v>
       </c>
@@ -4978,17 +4742,11 @@
       <c r="E8" s="15">
         <v>5926816.5809000004</v>
       </c>
-      <c r="F8" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F8" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>35</v>
       </c>
@@ -5004,17 +4762,11 @@
       <c r="E9" s="15">
         <v>5926821.4907999998</v>
       </c>
-      <c r="F9" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="H9" s="5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F9" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>29</v>
       </c>
@@ -5030,17 +4782,11 @@
       <c r="E10" s="15">
         <v>5926832.1205000002</v>
       </c>
-      <c r="F10" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F10" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>24</v>
       </c>
@@ -5056,17 +4802,11 @@
       <c r="E11" s="15">
         <v>5926841.9177000001</v>
       </c>
-      <c r="F11" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="H11" s="5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F11" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>28</v>
       </c>
@@ -5082,17 +4822,11 @@
       <c r="E12" s="15">
         <v>5926851.7503000004</v>
       </c>
-      <c r="F12" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="H12" s="5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F12" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>18</v>
       </c>
@@ -5108,17 +4842,11 @@
       <c r="E13" s="15">
         <v>5925672.8383999998</v>
       </c>
-      <c r="F13" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="H13" s="5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F13" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>11</v>
       </c>
@@ -5134,17 +4862,11 @@
       <c r="E14" s="15">
         <v>5925722.3081999999</v>
       </c>
-      <c r="F14" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="H14" s="5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F14" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>12</v>
       </c>
@@ -5160,17 +4882,11 @@
       <c r="E15" s="15">
         <v>5925744.102</v>
       </c>
-      <c r="F15" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="H15" s="5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F15" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>15</v>
       </c>
@@ -5186,17 +4902,11 @@
       <c r="E16" s="15">
         <v>5925598.8696999997</v>
       </c>
-      <c r="F16" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="H16" s="5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F16" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>16</v>
       </c>
@@ -5212,17 +4922,11 @@
       <c r="E17" s="15">
         <v>5925760.5027999999</v>
       </c>
-      <c r="F17" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="G17" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="H17" s="5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F17" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>21</v>
       </c>
@@ -5238,17 +4942,11 @@
       <c r="E18" s="15">
         <v>5925750.5869000005</v>
       </c>
-      <c r="F18" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="G18" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="H18" s="5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F18" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>9</v>
       </c>
@@ -5264,17 +4962,11 @@
       <c r="E19" s="15">
         <v>5925707.2302000001</v>
       </c>
-      <c r="F19" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="H19" s="5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F19" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>19</v>
       </c>
@@ -5290,17 +4982,11 @@
       <c r="E20" s="15">
         <v>5925473.7775999997</v>
       </c>
-      <c r="F20" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="G20" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="H20" s="5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F20" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
         <v>25</v>
       </c>
@@ -5316,17 +5002,11 @@
       <c r="E21" s="15">
         <v>5925538.8964</v>
       </c>
-      <c r="F21" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="G21" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="H21" s="5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F21" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>32</v>
       </c>
@@ -5342,17 +5022,11 @@
       <c r="E22" s="15">
         <v>5925738.2577999998</v>
       </c>
-      <c r="F22" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="G22" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="H22" s="5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F22" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
         <v>22</v>
       </c>
@@ -5368,17 +5042,11 @@
       <c r="E23" s="15">
         <v>5924550.3740999997</v>
       </c>
-      <c r="F23" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="G23" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="H23" s="5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F23" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
         <v>27</v>
       </c>
@@ -5394,17 +5062,11 @@
       <c r="E24" s="15">
         <v>5924530.9869999997</v>
       </c>
-      <c r="F24" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="G24" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="H24" s="5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F24" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
         <v>34</v>
       </c>
@@ -5420,17 +5082,11 @@
       <c r="E25" s="15">
         <v>5924621.1495000003</v>
       </c>
-      <c r="F25" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="G25" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="H25" s="5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F25" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
         <v>26</v>
       </c>
@@ -5446,17 +5102,11 @@
       <c r="E26" s="15">
         <v>5924472.1304000001</v>
       </c>
-      <c r="F26" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="G26" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="H26" s="5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F26" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
         <v>7</v>
       </c>
@@ -5472,17 +5122,11 @@
       <c r="E27" s="15">
         <v>5924652.8443</v>
       </c>
-      <c r="F27" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G27" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="H27" s="5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F27" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
         <v>13</v>
       </c>
@@ -5498,17 +5142,11 @@
       <c r="E28" s="15">
         <v>5924460.3476999998</v>
       </c>
-      <c r="F28" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="G28" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="H28" s="5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F28" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
         <v>23</v>
       </c>
@@ -5524,17 +5162,11 @@
       <c r="E29" s="15">
         <v>5924363.7493000003</v>
       </c>
-      <c r="F29" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G29" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="H29" s="5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F29" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
         <v>38</v>
       </c>
@@ -5550,17 +5182,11 @@
       <c r="E30" s="15">
         <v>5923335.0530000003</v>
       </c>
-      <c r="F30" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="G30" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="H30" s="5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F30" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
         <v>37</v>
       </c>
@@ -5576,17 +5202,11 @@
       <c r="E31" s="15">
         <v>5922980.8535000002</v>
       </c>
-      <c r="F31" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="G31" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="H31" s="5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F31" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
         <v>31</v>
       </c>
@@ -5602,17 +5222,11 @@
       <c r="E32" s="15">
         <v>5923540.4664000003</v>
       </c>
-      <c r="F32" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="G32" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="H32" s="5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F32" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
         <v>39</v>
       </c>
@@ -5628,17 +5242,11 @@
       <c r="E33" s="15">
         <v>5923286.1697000004</v>
       </c>
-      <c r="F33" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G33" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="H33" s="5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F33" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
         <v>53</v>
       </c>
@@ -5654,17 +5262,11 @@
       <c r="E34" s="15">
         <v>5923568.3879000004</v>
       </c>
-      <c r="F34" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G34" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="H34" s="5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F34" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
         <v>42</v>
       </c>
@@ -5680,17 +5282,11 @@
       <c r="E35" s="15">
         <v>5923406.2419999996</v>
       </c>
-      <c r="F35" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G35" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="H35" s="5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F35" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
         <v>41</v>
       </c>
@@ -5706,17 +5302,11 @@
       <c r="E36" s="15">
         <v>5923167.5865000002</v>
       </c>
-      <c r="F36" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G36" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="H36" s="5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F36" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
         <v>33</v>
       </c>
@@ -5732,17 +5322,11 @@
       <c r="E37" s="15">
         <v>5923221.8696999997</v>
       </c>
-      <c r="F37" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="G37" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="H37" s="5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F37" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
         <v>6</v>
       </c>
@@ -5758,17 +5342,11 @@
       <c r="E38" s="15">
         <v>5922267.1327</v>
       </c>
-      <c r="F38" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="G38" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="H38" s="5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F38" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" s="1" t="s">
         <v>44</v>
       </c>
@@ -5784,17 +5362,11 @@
       <c r="E39" s="15">
         <v>5921798.2410000004</v>
       </c>
-      <c r="F39" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="G39" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="H39" s="5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F39" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
         <v>36</v>
       </c>
@@ -5810,17 +5382,11 @@
       <c r="E40" s="15">
         <v>5922377.7856000001</v>
       </c>
-      <c r="F40" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="G40" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="H40" s="5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F40" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41" s="1" t="s">
         <v>30</v>
       </c>
@@ -5836,17 +5402,11 @@
       <c r="E41" s="15">
         <v>5922155.3957000002</v>
       </c>
-      <c r="F41" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="G41" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="H41" s="5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F41" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42" s="1" t="s">
         <v>45</v>
       </c>
@@ -5862,17 +5422,11 @@
       <c r="E42" s="15">
         <v>5922329.3293000003</v>
       </c>
-      <c r="F42" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G42" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="H42" s="5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F42" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
         <v>40</v>
       </c>
@@ -5888,17 +5442,11 @@
       <c r="E43" s="15">
         <v>5921269.5873999996</v>
       </c>
-      <c r="F43" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="G43" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="H43" s="5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F43" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44" s="1" t="s">
         <v>46</v>
       </c>
@@ -5914,17 +5462,11 @@
       <c r="E44" s="15">
         <v>5920800.6169999996</v>
       </c>
-      <c r="F44" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="G44" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="H44" s="5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F44" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
         <v>43</v>
       </c>
@@ -5940,17 +5482,11 @@
       <c r="E45" s="15">
         <v>5921383.6398</v>
       </c>
-      <c r="F45" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="G45" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="H45" s="5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F45" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
         <v>50</v>
       </c>
@@ -5966,17 +5502,11 @@
       <c r="E46" s="15">
         <v>5921209.0383000001</v>
       </c>
-      <c r="F46" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G46" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="H46" s="5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F46" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
         <v>51</v>
       </c>
@@ -5992,17 +5522,11 @@
       <c r="E47" s="15">
         <v>5921441.3432999998</v>
       </c>
-      <c r="F47" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G47" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="H47" s="5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F47" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
         <v>52</v>
       </c>
@@ -6018,17 +5542,11 @@
       <c r="E48" s="15">
         <v>5921513.1471999995</v>
       </c>
-      <c r="F48" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G48" s="5" t="s">
+      <c r="F48" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="H48" s="5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49" s="1" t="s">
         <v>47</v>
       </c>
@@ -6044,17 +5562,11 @@
       <c r="E49" s="15">
         <v>5920292.7520000003</v>
       </c>
-      <c r="F49" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="G49" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="H49" s="5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F49" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" s="1" t="s">
         <v>48</v>
       </c>
@@ -6070,17 +5582,11 @@
       <c r="E50" s="15">
         <v>5919830.1629999997</v>
       </c>
-      <c r="F50" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="G50" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="H50" s="5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F50" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" s="1" t="s">
         <v>49</v>
       </c>
@@ -6096,25 +5602,19 @@
       <c r="E51" s="15">
         <v>5920298.3925000001</v>
       </c>
-      <c r="F51" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="G51" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="H51" s="5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F51" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" s="21" t="s">
-        <v>116</v>
+        <v>65</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>116</v>
+        <v>65</v>
       </c>
       <c r="D52" s="15">
         <v>451560.92599999998</v>
@@ -6122,20 +5622,18 @@
       <c r="E52" s="22">
         <v>5922304.4649</v>
       </c>
-      <c r="F52" s="4"/>
-      <c r="G52" s="23"/>
-      <c r="H52" s="23"/>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F52" s="23"/>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A54" s="3"/>
       <c r="B54" s="3"/>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57" s="3"/>
       <c r="B57" s="3"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H1" xr:uid="{A82EA8D4-BAA5-468E-B97E-DC4F4ED9B933}"/>
+  <autoFilter ref="A1:F1" xr:uid="{A82EA8D4-BAA5-468E-B97E-DC4F4ED9B933}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -6170,25 +5668,25 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
-        <v>188</v>
+        <v>137</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>189</v>
+        <v>138</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>190</v>
+        <v>139</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>189</v>
+        <v>138</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>190</v>
+        <v>139</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>189</v>
+        <v>138</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>190</v>
+        <v>139</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
@@ -7125,7 +6623,7 @@
         <v>47606</v>
       </c>
       <c r="C35" s="9">
-        <f t="shared" ref="C35:C66" si="6">B35+1</f>
+        <f t="shared" ref="C35:C52" si="6">B35+1</f>
         <v>47607</v>
       </c>
       <c r="D35" s="9">
@@ -7133,7 +6631,7 @@
         <v>47718.399999999907</v>
       </c>
       <c r="E35" s="9">
-        <f t="shared" ref="E35:E66" si="7">D35+0.7</f>
+        <f t="shared" ref="E35:E57" si="7">D35+0.7</f>
         <v>47719.099999999904</v>
       </c>
       <c r="F35" s="9">
@@ -7734,6 +7232,32 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Revised xmlns="7b1e1d97-de89-451e-b61e-3a612707828f">false</Revised>
+    <_Flow_SignoffStatus xmlns="7b1e1d97-de89-451e-b61e-3a612707828f" xsi:nil="true"/>
+    <IconOverlay xmlns="http://schemas.microsoft.com/sharepoint/v4" xsi:nil="true"/>
+    <DateandTime xmlns="7b1e1d97-de89-451e-b61e-3a612707828f" xsi:nil="true"/>
+    <TranslatedLang xmlns="7b1e1d97-de89-451e-b61e-3a612707828f" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7b1e1d97-de89-451e-b61e-3a612707828f">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="fb957374-73fb-46c8-b1d5-5557a51ca38a" xsi:nil="true"/>
+    <OEM xmlns="7b1e1d97-de89-451e-b61e-3a612707828f" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101004B4B1D761BDB6B498A1DC5A0D78900EE" ma:contentTypeVersion="26" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="78345c13f88d78bd560ff02a76daed41">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7b1e1d97-de89-451e-b61e-3a612707828f" xmlns:ns3="5b6d62e9-fedc-43d0-83d3-3983de244cac" xmlns:ns4="fb957374-73fb-46c8-b1d5-5557a51ca38a" xmlns:ns5="http://schemas.microsoft.com/sharepoint/v4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c745cdac93650d4e9673cc66f9377fdc" ns2:_="" ns3:_="" ns4:_="" ns5:_="">
     <xsd:import namespace="7b1e1d97-de89-451e-b61e-3a612707828f"/>
@@ -8043,33 +7567,34 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Revised xmlns="7b1e1d97-de89-451e-b61e-3a612707828f">false</Revised>
-    <_Flow_SignoffStatus xmlns="7b1e1d97-de89-451e-b61e-3a612707828f" xsi:nil="true"/>
-    <IconOverlay xmlns="http://schemas.microsoft.com/sharepoint/v4" xsi:nil="true"/>
-    <DateandTime xmlns="7b1e1d97-de89-451e-b61e-3a612707828f" xsi:nil="true"/>
-    <TranslatedLang xmlns="7b1e1d97-de89-451e-b61e-3a612707828f" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7b1e1d97-de89-451e-b61e-3a612707828f">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="fb957374-73fb-46c8-b1d5-5557a51ca38a" xsi:nil="true"/>
-    <OEM xmlns="7b1e1d97-de89-451e-b61e-3a612707828f" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EBE4A505-FD97-4F62-A54E-794D67C3C89E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="7b1e1d97-de89-451e-b61e-3a612707828f"/>
+    <ds:schemaRef ds:uri="5b6d62e9-fedc-43d0-83d3-3983de244cac"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v4"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="fb957374-73fb-46c8-b1d5-5557a51ca38a"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D87E93EE-9EE0-4F81-BCAE-80D6FC49D1B7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2068500C-071F-4C15-A3AC-7E2EA9766AFC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -8090,33 +7615,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EBE4A505-FD97-4F62-A54E-794D67C3C89E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="7b1e1d97-de89-451e-b61e-3a612707828f"/>
-    <ds:schemaRef ds:uri="5b6d62e9-fedc-43d0-83d3-3983de244cac"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v4"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="fb957374-73fb-46c8-b1d5-5557a51ca38a"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D87E93EE-9EE0-4F81-BCAE-80D6FC49D1B7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{f481d56f-c63d-4d74-8406-d64e74f44395}" enabled="0" method="" siteId="{f481d56f-c63d-4d74-8406-d64e74f44395}" removed="1"/>
